--- a/templates/PV_MODELE.xlsx
+++ b/templates/PV_MODELE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PV_ECHAFAUDAGE\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4092D95-BEEC-402C-AD80-D017B825B27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1ED0F91-AD97-4DFC-B0AA-99A940C07225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Référence source" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Formulaire!$A$1:$AR$137</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Formulaire!$A$1:$AR$124</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -1041,18 +1041,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1084,6 +1072,36 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1099,11 +1117,23 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1127,12 +1157,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1223,24 +1247,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1363,12 +1369,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1752,7 +1752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR137"/>
+  <dimension ref="A1:AR124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.08984375" style="2" bestFit="1" customWidth="1"/>
@@ -1782,104 +1782,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
-      <c r="Z1" s="82"/>
-      <c r="AA1" s="100"/>
-      <c r="AB1" s="124" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="89"/>
+      <c r="Q1" s="89"/>
+      <c r="R1" s="89"/>
+      <c r="S1" s="89"/>
+      <c r="T1" s="89"/>
+      <c r="U1" s="89"/>
+      <c r="V1" s="89"/>
+      <c r="W1" s="89"/>
+      <c r="X1" s="89"/>
+      <c r="Y1" s="89"/>
+      <c r="Z1" s="90"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="AC1" s="125"/>
-      <c r="AD1" s="125"/>
-      <c r="AE1" s="125"/>
-      <c r="AF1" s="125"/>
-      <c r="AG1" s="125"/>
-      <c r="AH1" s="125"/>
-      <c r="AI1" s="125"/>
-      <c r="AJ1" s="125"/>
-      <c r="AK1" s="125"/>
-      <c r="AL1" s="125"/>
-      <c r="AM1" s="125"/>
-      <c r="AN1" s="125"/>
-      <c r="AO1" s="126"/>
-      <c r="AP1" s="133" t="s">
+      <c r="AC1" s="127"/>
+      <c r="AD1" s="127"/>
+      <c r="AE1" s="127"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="127"/>
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="127"/>
+      <c r="AK1" s="127"/>
+      <c r="AL1" s="127"/>
+      <c r="AM1" s="127"/>
+      <c r="AN1" s="127"/>
+      <c r="AO1" s="128"/>
+      <c r="AP1" s="135" t="s">
         <v>1</v>
       </c>
-      <c r="AQ1" s="133"/>
-      <c r="AR1" s="135" t="s">
+      <c r="AQ1" s="135"/>
+      <c r="AR1" s="137" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:44" ht="11" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="83"/>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="84"/>
-      <c r="R2" s="84"/>
-      <c r="S2" s="84"/>
-      <c r="T2" s="84"/>
-      <c r="U2" s="84"/>
-      <c r="V2" s="84"/>
-      <c r="W2" s="84"/>
-      <c r="X2" s="84"/>
-      <c r="Y2" s="84"/>
-      <c r="Z2" s="85"/>
-      <c r="AA2" s="101"/>
-      <c r="AB2" s="127"/>
-      <c r="AC2" s="128"/>
-      <c r="AD2" s="128"/>
-      <c r="AE2" s="128"/>
-      <c r="AF2" s="128"/>
-      <c r="AG2" s="128"/>
-      <c r="AH2" s="128"/>
-      <c r="AI2" s="128"/>
-      <c r="AJ2" s="128"/>
-      <c r="AK2" s="128"/>
-      <c r="AL2" s="128"/>
-      <c r="AM2" s="128"/>
-      <c r="AN2" s="128"/>
-      <c r="AO2" s="129"/>
-      <c r="AP2" s="134"/>
-      <c r="AQ2" s="134"/>
-      <c r="AR2" s="136"/>
+      <c r="A2" s="91"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+      <c r="R2" s="92"/>
+      <c r="S2" s="92"/>
+      <c r="T2" s="92"/>
+      <c r="U2" s="92"/>
+      <c r="V2" s="92"/>
+      <c r="W2" s="92"/>
+      <c r="X2" s="92"/>
+      <c r="Y2" s="92"/>
+      <c r="Z2" s="93"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="129"/>
+      <c r="AC2" s="130"/>
+      <c r="AD2" s="130"/>
+      <c r="AE2" s="130"/>
+      <c r="AF2" s="130"/>
+      <c r="AG2" s="130"/>
+      <c r="AH2" s="130"/>
+      <c r="AI2" s="130"/>
+      <c r="AJ2" s="130"/>
+      <c r="AK2" s="130"/>
+      <c r="AL2" s="130"/>
+      <c r="AM2" s="130"/>
+      <c r="AN2" s="130"/>
+      <c r="AO2" s="131"/>
+      <c r="AP2" s="136"/>
+      <c r="AQ2" s="136"/>
+      <c r="AR2" s="138"/>
     </row>
     <row r="3" spans="1:44" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
@@ -1908,177 +1908,177 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
       <c r="Z3" s="5"/>
-      <c r="AA3" s="101"/>
-      <c r="AB3" s="130"/>
-      <c r="AC3" s="131"/>
-      <c r="AD3" s="131"/>
-      <c r="AE3" s="131"/>
-      <c r="AF3" s="131"/>
-      <c r="AG3" s="131"/>
-      <c r="AH3" s="131"/>
-      <c r="AI3" s="131"/>
-      <c r="AJ3" s="131"/>
-      <c r="AK3" s="131"/>
-      <c r="AL3" s="131"/>
-      <c r="AM3" s="131"/>
-      <c r="AN3" s="131"/>
-      <c r="AO3" s="132"/>
+      <c r="AA3" s="41"/>
+      <c r="AB3" s="132"/>
+      <c r="AC3" s="133"/>
+      <c r="AD3" s="133"/>
+      <c r="AE3" s="133"/>
+      <c r="AF3" s="133"/>
+      <c r="AG3" s="133"/>
+      <c r="AH3" s="133"/>
+      <c r="AI3" s="133"/>
+      <c r="AJ3" s="133"/>
+      <c r="AK3" s="133"/>
+      <c r="AL3" s="133"/>
+      <c r="AM3" s="133"/>
+      <c r="AN3" s="133"/>
+      <c r="AO3" s="134"/>
       <c r="AP3" s="24" t="s">
         <v>3</v>
       </c>
       <c r="AQ3" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="AR3" s="137"/>
+      <c r="AR3" s="139"/>
     </row>
     <row r="4" spans="1:44" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="40"/>
-      <c r="U4" s="40"/>
-      <c r="V4" s="40"/>
-      <c r="W4" s="40"/>
-      <c r="X4" s="40"/>
-      <c r="Y4" s="40"/>
-      <c r="Z4" s="41"/>
-      <c r="AA4" s="101"/>
-      <c r="AB4" s="64" t="s">
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="37"/>
+      <c r="AA4" s="41"/>
+      <c r="AB4" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="AC4" s="90"/>
-      <c r="AD4" s="90"/>
-      <c r="AE4" s="90"/>
-      <c r="AF4" s="90"/>
-      <c r="AG4" s="91"/>
-      <c r="AH4" s="92" t="s">
+      <c r="AC4" s="98"/>
+      <c r="AD4" s="98"/>
+      <c r="AE4" s="98"/>
+      <c r="AF4" s="98"/>
+      <c r="AG4" s="99"/>
+      <c r="AH4" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="AI4" s="32"/>
-      <c r="AJ4" s="32"/>
-      <c r="AK4" s="32"/>
-      <c r="AL4" s="32"/>
-      <c r="AM4" s="32"/>
-      <c r="AN4" s="32"/>
-      <c r="AO4" s="32"/>
-      <c r="AP4" s="138"/>
-      <c r="AQ4" s="140"/>
-      <c r="AR4" s="142"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="28"/>
+      <c r="AK4" s="28"/>
+      <c r="AL4" s="28"/>
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="28"/>
+      <c r="AO4" s="28"/>
+      <c r="AP4" s="140"/>
+      <c r="AQ4" s="142"/>
+      <c r="AR4" s="144"/>
     </row>
     <row r="5" spans="1:44" ht="29" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="40"/>
-      <c r="T5" s="40"/>
-      <c r="U5" s="40"/>
-      <c r="V5" s="40"/>
-      <c r="W5" s="40"/>
-      <c r="X5" s="40"/>
-      <c r="Y5" s="40"/>
-      <c r="Z5" s="41"/>
-      <c r="AA5" s="101"/>
-      <c r="AB5" s="30"/>
-      <c r="AC5" s="28"/>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="34"/>
-      <c r="AI5" s="34"/>
-      <c r="AJ5" s="34"/>
-      <c r="AK5" s="34"/>
-      <c r="AL5" s="34"/>
-      <c r="AM5" s="34"/>
-      <c r="AN5" s="34"/>
-      <c r="AO5" s="34"/>
-      <c r="AP5" s="139"/>
-      <c r="AQ5" s="141"/>
-      <c r="AR5" s="143"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="36"/>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36"/>
+      <c r="X5" s="36"/>
+      <c r="Y5" s="36"/>
+      <c r="Z5" s="37"/>
+      <c r="AA5" s="41"/>
+      <c r="AB5" s="61"/>
+      <c r="AC5" s="56"/>
+      <c r="AD5" s="56"/>
+      <c r="AE5" s="56"/>
+      <c r="AF5" s="56"/>
+      <c r="AG5" s="57"/>
+      <c r="AH5" s="30"/>
+      <c r="AI5" s="30"/>
+      <c r="AJ5" s="30"/>
+      <c r="AK5" s="30"/>
+      <c r="AL5" s="30"/>
+      <c r="AM5" s="30"/>
+      <c r="AN5" s="30"/>
+      <c r="AO5" s="30"/>
+      <c r="AP5" s="141"/>
+      <c r="AQ5" s="143"/>
+      <c r="AR5" s="145"/>
     </row>
     <row r="6" spans="1:44" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="40"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="40"/>
-      <c r="W6" s="40"/>
-      <c r="X6" s="40"/>
-      <c r="Y6" s="40"/>
-      <c r="Z6" s="41"/>
-      <c r="AA6" s="101"/>
-      <c r="AB6" s="27" t="s">
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="36"/>
+      <c r="Y6" s="36"/>
+      <c r="Z6" s="37"/>
+      <c r="AA6" s="41"/>
+      <c r="AB6" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="28"/>
-      <c r="AE6" s="28"/>
-      <c r="AF6" s="28"/>
-      <c r="AG6" s="29"/>
-      <c r="AH6" s="33" t="s">
+      <c r="AC6" s="56"/>
+      <c r="AD6" s="56"/>
+      <c r="AE6" s="56"/>
+      <c r="AF6" s="56"/>
+      <c r="AG6" s="57"/>
+      <c r="AH6" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="AI6" s="34"/>
-      <c r="AJ6" s="34"/>
-      <c r="AK6" s="34"/>
-      <c r="AL6" s="34"/>
-      <c r="AM6" s="34"/>
-      <c r="AN6" s="34"/>
-      <c r="AO6" s="35"/>
+      <c r="AI6" s="30"/>
+      <c r="AJ6" s="30"/>
+      <c r="AK6" s="30"/>
+      <c r="AL6" s="30"/>
+      <c r="AM6" s="30"/>
+      <c r="AN6" s="30"/>
+      <c r="AO6" s="31"/>
       <c r="AP6" s="8"/>
       <c r="AQ6" s="8"/>
       <c r="AR6" s="9"/>
@@ -2110,23 +2110,23 @@
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
       <c r="Z7" s="5"/>
-      <c r="AA7" s="101"/>
-      <c r="AB7" s="30"/>
-      <c r="AC7" s="28"/>
-      <c r="AD7" s="28"/>
-      <c r="AE7" s="28"/>
-      <c r="AF7" s="28"/>
-      <c r="AG7" s="29"/>
-      <c r="AH7" s="33" t="s">
+      <c r="AA7" s="41"/>
+      <c r="AB7" s="61"/>
+      <c r="AC7" s="56"/>
+      <c r="AD7" s="56"/>
+      <c r="AE7" s="56"/>
+      <c r="AF7" s="56"/>
+      <c r="AG7" s="57"/>
+      <c r="AH7" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="AI7" s="34"/>
-      <c r="AJ7" s="34"/>
-      <c r="AK7" s="34"/>
-      <c r="AL7" s="34"/>
-      <c r="AM7" s="34"/>
-      <c r="AN7" s="34"/>
-      <c r="AO7" s="35"/>
+      <c r="AI7" s="30"/>
+      <c r="AJ7" s="30"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="30"/>
+      <c r="AM7" s="30"/>
+      <c r="AN7" s="30"/>
+      <c r="AO7" s="31"/>
       <c r="AP7" s="8"/>
       <c r="AQ7" s="8"/>
       <c r="AR7" s="9"/>
@@ -2135,48 +2135,48 @@
       <c r="A8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="40"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="40"/>
-      <c r="W8" s="40"/>
-      <c r="X8" s="40"/>
-      <c r="Y8" s="40"/>
-      <c r="Z8" s="41"/>
-      <c r="AA8" s="101"/>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="28"/>
-      <c r="AD8" s="28"/>
-      <c r="AE8" s="28"/>
-      <c r="AF8" s="28"/>
-      <c r="AG8" s="29"/>
-      <c r="AH8" s="33" t="s">
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
+      <c r="S8" s="36"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="36"/>
+      <c r="V8" s="36"/>
+      <c r="W8" s="36"/>
+      <c r="X8" s="36"/>
+      <c r="Y8" s="36"/>
+      <c r="Z8" s="37"/>
+      <c r="AA8" s="41"/>
+      <c r="AB8" s="61"/>
+      <c r="AC8" s="56"/>
+      <c r="AD8" s="56"/>
+      <c r="AE8" s="56"/>
+      <c r="AF8" s="56"/>
+      <c r="AG8" s="57"/>
+      <c r="AH8" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="AI8" s="34"/>
-      <c r="AJ8" s="34"/>
-      <c r="AK8" s="34"/>
-      <c r="AL8" s="34"/>
-      <c r="AM8" s="34"/>
-      <c r="AN8" s="34"/>
-      <c r="AO8" s="35"/>
+      <c r="AI8" s="30"/>
+      <c r="AJ8" s="30"/>
+      <c r="AK8" s="30"/>
+      <c r="AL8" s="30"/>
+      <c r="AM8" s="30"/>
+      <c r="AN8" s="30"/>
+      <c r="AO8" s="31"/>
       <c r="AP8" s="8"/>
       <c r="AQ8" s="8"/>
       <c r="AR8" s="9"/>
@@ -2185,50 +2185,50 @@
       <c r="A9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="40"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
       <c r="S9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="101"/>
-      <c r="AB9" s="30"/>
-      <c r="AC9" s="28"/>
-      <c r="AD9" s="28"/>
-      <c r="AE9" s="28"/>
-      <c r="AF9" s="28"/>
-      <c r="AG9" s="29"/>
-      <c r="AH9" s="33" t="s">
+      <c r="T9" s="32"/>
+      <c r="U9" s="32"/>
+      <c r="V9" s="32"/>
+      <c r="W9" s="32"/>
+      <c r="X9" s="32"/>
+      <c r="Y9" s="32"/>
+      <c r="Z9" s="33"/>
+      <c r="AA9" s="41"/>
+      <c r="AB9" s="61"/>
+      <c r="AC9" s="56"/>
+      <c r="AD9" s="56"/>
+      <c r="AE9" s="56"/>
+      <c r="AF9" s="56"/>
+      <c r="AG9" s="57"/>
+      <c r="AH9" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="AI9" s="34"/>
-      <c r="AJ9" s="34"/>
-      <c r="AK9" s="34"/>
-      <c r="AL9" s="34"/>
-      <c r="AM9" s="34"/>
-      <c r="AN9" s="34"/>
-      <c r="AO9" s="35"/>
+      <c r="AI9" s="30"/>
+      <c r="AJ9" s="30"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="30"/>
+      <c r="AM9" s="30"/>
+      <c r="AN9" s="30"/>
+      <c r="AO9" s="31"/>
       <c r="AP9" s="8"/>
       <c r="AQ9" s="8"/>
       <c r="AR9" s="9"/>
@@ -2260,23 +2260,23 @@
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
       <c r="Z10" s="5"/>
-      <c r="AA10" s="101"/>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="28"/>
-      <c r="AD10" s="28"/>
-      <c r="AE10" s="28"/>
-      <c r="AF10" s="28"/>
-      <c r="AG10" s="29"/>
-      <c r="AH10" s="33" t="s">
+      <c r="AA10" s="41"/>
+      <c r="AB10" s="61"/>
+      <c r="AC10" s="56"/>
+      <c r="AD10" s="56"/>
+      <c r="AE10" s="56"/>
+      <c r="AF10" s="56"/>
+      <c r="AG10" s="57"/>
+      <c r="AH10" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="AI10" s="34"/>
-      <c r="AJ10" s="34"/>
-      <c r="AK10" s="34"/>
-      <c r="AL10" s="34"/>
-      <c r="AM10" s="34"/>
-      <c r="AN10" s="34"/>
-      <c r="AO10" s="35"/>
+      <c r="AI10" s="30"/>
+      <c r="AJ10" s="30"/>
+      <c r="AK10" s="30"/>
+      <c r="AL10" s="30"/>
+      <c r="AM10" s="30"/>
+      <c r="AN10" s="30"/>
+      <c r="AO10" s="31"/>
       <c r="AP10" s="8"/>
       <c r="AQ10" s="8"/>
       <c r="AR10" s="9"/>
@@ -2285,102 +2285,102 @@
       <c r="A11" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="36"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="36"/>
-      <c r="V11" s="36"/>
-      <c r="W11" s="36"/>
-      <c r="X11" s="36"/>
-      <c r="Y11" s="36"/>
-      <c r="Z11" s="37"/>
-      <c r="AA11" s="101"/>
-      <c r="AB11" s="30"/>
-      <c r="AC11" s="28"/>
-      <c r="AD11" s="28"/>
-      <c r="AE11" s="28"/>
-      <c r="AF11" s="28"/>
-      <c r="AG11" s="29"/>
-      <c r="AH11" s="33" t="s">
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="32"/>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="32"/>
+      <c r="T11" s="32"/>
+      <c r="U11" s="32"/>
+      <c r="V11" s="32"/>
+      <c r="W11" s="32"/>
+      <c r="X11" s="32"/>
+      <c r="Y11" s="32"/>
+      <c r="Z11" s="33"/>
+      <c r="AA11" s="41"/>
+      <c r="AB11" s="61"/>
+      <c r="AC11" s="56"/>
+      <c r="AD11" s="56"/>
+      <c r="AE11" s="56"/>
+      <c r="AF11" s="56"/>
+      <c r="AG11" s="57"/>
+      <c r="AH11" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AI11" s="34"/>
-      <c r="AJ11" s="34"/>
-      <c r="AK11" s="34"/>
-      <c r="AL11" s="34"/>
-      <c r="AM11" s="34"/>
-      <c r="AN11" s="34"/>
-      <c r="AO11" s="35"/>
-      <c r="AP11" s="103"/>
-      <c r="AQ11" s="104"/>
+      <c r="AI11" s="30"/>
+      <c r="AJ11" s="30"/>
+      <c r="AK11" s="30"/>
+      <c r="AL11" s="30"/>
+      <c r="AM11" s="30"/>
+      <c r="AN11" s="30"/>
+      <c r="AO11" s="31"/>
+      <c r="AP11" s="105"/>
+      <c r="AQ11" s="106"/>
       <c r="AR11" s="9"/>
     </row>
     <row r="12" spans="1:44" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="40"/>
-      <c r="M12" s="40"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="40"/>
-      <c r="R12" s="40"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
       <c r="S12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="T12" s="40"/>
-      <c r="U12" s="40"/>
-      <c r="V12" s="40"/>
-      <c r="W12" s="40"/>
-      <c r="X12" s="40"/>
-      <c r="Y12" s="40"/>
-      <c r="Z12" s="41"/>
-      <c r="AA12" s="101"/>
-      <c r="AB12" s="27" t="s">
+      <c r="T12" s="36"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="36"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="36"/>
+      <c r="Y12" s="36"/>
+      <c r="Z12" s="37"/>
+      <c r="AA12" s="41"/>
+      <c r="AB12" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AC12" s="28"/>
-      <c r="AD12" s="28"/>
-      <c r="AE12" s="28"/>
-      <c r="AF12" s="28"/>
-      <c r="AG12" s="29"/>
-      <c r="AH12" s="33" t="s">
+      <c r="AC12" s="56"/>
+      <c r="AD12" s="56"/>
+      <c r="AE12" s="56"/>
+      <c r="AF12" s="56"/>
+      <c r="AG12" s="57"/>
+      <c r="AH12" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="AI12" s="34"/>
-      <c r="AJ12" s="34"/>
-      <c r="AK12" s="34"/>
-      <c r="AL12" s="34"/>
-      <c r="AM12" s="34"/>
-      <c r="AN12" s="34"/>
-      <c r="AO12" s="35"/>
+      <c r="AI12" s="30"/>
+      <c r="AJ12" s="30"/>
+      <c r="AK12" s="30"/>
+      <c r="AL12" s="30"/>
+      <c r="AM12" s="30"/>
+      <c r="AN12" s="30"/>
+      <c r="AO12" s="31"/>
       <c r="AP12" s="8"/>
       <c r="AQ12" s="8"/>
       <c r="AR12" s="9"/>
@@ -2389,48 +2389,48 @@
       <c r="A13" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="75"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="75"/>
-      <c r="K13" s="75"/>
-      <c r="L13" s="75"/>
-      <c r="M13" s="75"/>
-      <c r="N13" s="75"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="75"/>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="75"/>
-      <c r="T13" s="75"/>
-      <c r="U13" s="75"/>
-      <c r="V13" s="75"/>
-      <c r="W13" s="75"/>
-      <c r="X13" s="75"/>
-      <c r="Y13" s="75"/>
-      <c r="Z13" s="76"/>
-      <c r="AA13" s="101"/>
-      <c r="AB13" s="30"/>
-      <c r="AC13" s="28"/>
-      <c r="AD13" s="28"/>
-      <c r="AE13" s="28"/>
-      <c r="AF13" s="28"/>
-      <c r="AG13" s="29"/>
-      <c r="AH13" s="33" t="s">
+      <c r="B13" s="83"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="83"/>
+      <c r="K13" s="83"/>
+      <c r="L13" s="83"/>
+      <c r="M13" s="83"/>
+      <c r="N13" s="83"/>
+      <c r="O13" s="83"/>
+      <c r="P13" s="83"/>
+      <c r="Q13" s="83"/>
+      <c r="R13" s="83"/>
+      <c r="S13" s="83"/>
+      <c r="T13" s="83"/>
+      <c r="U13" s="83"/>
+      <c r="V13" s="83"/>
+      <c r="W13" s="83"/>
+      <c r="X13" s="83"/>
+      <c r="Y13" s="83"/>
+      <c r="Z13" s="84"/>
+      <c r="AA13" s="41"/>
+      <c r="AB13" s="61"/>
+      <c r="AC13" s="56"/>
+      <c r="AD13" s="56"/>
+      <c r="AE13" s="56"/>
+      <c r="AF13" s="56"/>
+      <c r="AG13" s="57"/>
+      <c r="AH13" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="AI13" s="34"/>
-      <c r="AJ13" s="34"/>
-      <c r="AK13" s="34"/>
-      <c r="AL13" s="34"/>
-      <c r="AM13" s="34"/>
-      <c r="AN13" s="34"/>
-      <c r="AO13" s="35"/>
+      <c r="AI13" s="30"/>
+      <c r="AJ13" s="30"/>
+      <c r="AK13" s="30"/>
+      <c r="AL13" s="30"/>
+      <c r="AM13" s="30"/>
+      <c r="AN13" s="30"/>
+      <c r="AO13" s="31"/>
       <c r="AP13" s="8"/>
       <c r="AQ13" s="8"/>
       <c r="AR13" s="9"/>
@@ -2439,100 +2439,100 @@
       <c r="A14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="38"/>
-      <c r="P14" s="38"/>
-      <c r="Q14" s="38"/>
-      <c r="R14" s="38"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="34"/>
+      <c r="M14" s="34"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="34"/>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34"/>
       <c r="S14" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="38"/>
-      <c r="Y14" s="38"/>
-      <c r="Z14" s="39"/>
-      <c r="AA14" s="101"/>
-      <c r="AB14" s="30"/>
-      <c r="AC14" s="28"/>
-      <c r="AD14" s="28"/>
-      <c r="AE14" s="28"/>
-      <c r="AF14" s="28"/>
-      <c r="AG14" s="29"/>
-      <c r="AH14" s="33" t="s">
+      <c r="T14" s="34"/>
+      <c r="U14" s="34"/>
+      <c r="V14" s="34"/>
+      <c r="W14" s="34"/>
+      <c r="X14" s="34"/>
+      <c r="Y14" s="34"/>
+      <c r="Z14" s="35"/>
+      <c r="AA14" s="41"/>
+      <c r="AB14" s="61"/>
+      <c r="AC14" s="56"/>
+      <c r="AD14" s="56"/>
+      <c r="AE14" s="56"/>
+      <c r="AF14" s="56"/>
+      <c r="AG14" s="57"/>
+      <c r="AH14" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="AI14" s="34"/>
-      <c r="AJ14" s="34"/>
-      <c r="AK14" s="34"/>
-      <c r="AL14" s="34"/>
-      <c r="AM14" s="34"/>
-      <c r="AN14" s="34"/>
-      <c r="AO14" s="35"/>
+      <c r="AI14" s="30"/>
+      <c r="AJ14" s="30"/>
+      <c r="AK14" s="30"/>
+      <c r="AL14" s="30"/>
+      <c r="AM14" s="30"/>
+      <c r="AN14" s="30"/>
+      <c r="AO14" s="31"/>
       <c r="AP14" s="8"/>
       <c r="AQ14" s="8"/>
       <c r="AR14" s="9"/>
     </row>
     <row r="15" spans="1:44" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="62"/>
-      <c r="L15" s="62"/>
-      <c r="M15" s="62"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="62"/>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="62"/>
-      <c r="S15" s="62"/>
-      <c r="T15" s="62"/>
-      <c r="U15" s="62"/>
-      <c r="V15" s="62"/>
-      <c r="W15" s="62"/>
-      <c r="X15" s="62"/>
-      <c r="Y15" s="62"/>
-      <c r="Z15" s="145"/>
-      <c r="AA15" s="101"/>
-      <c r="AB15" s="30"/>
-      <c r="AC15" s="28"/>
-      <c r="AD15" s="28"/>
-      <c r="AE15" s="28"/>
-      <c r="AF15" s="28"/>
-      <c r="AG15" s="29"/>
-      <c r="AH15" s="33" t="s">
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="45"/>
+      <c r="M15" s="45"/>
+      <c r="N15" s="45"/>
+      <c r="O15" s="45"/>
+      <c r="P15" s="45"/>
+      <c r="Q15" s="45"/>
+      <c r="R15" s="45"/>
+      <c r="S15" s="45"/>
+      <c r="T15" s="45"/>
+      <c r="U15" s="45"/>
+      <c r="V15" s="45"/>
+      <c r="W15" s="45"/>
+      <c r="X15" s="45"/>
+      <c r="Y15" s="45"/>
+      <c r="Z15" s="46"/>
+      <c r="AA15" s="41"/>
+      <c r="AB15" s="61"/>
+      <c r="AC15" s="56"/>
+      <c r="AD15" s="56"/>
+      <c r="AE15" s="56"/>
+      <c r="AF15" s="56"/>
+      <c r="AG15" s="57"/>
+      <c r="AH15" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="AI15" s="34"/>
-      <c r="AJ15" s="34"/>
-      <c r="AK15" s="34"/>
-      <c r="AL15" s="34"/>
-      <c r="AM15" s="34"/>
-      <c r="AN15" s="34"/>
-      <c r="AO15" s="35"/>
+      <c r="AI15" s="30"/>
+      <c r="AJ15" s="30"/>
+      <c r="AK15" s="30"/>
+      <c r="AL15" s="30"/>
+      <c r="AM15" s="30"/>
+      <c r="AN15" s="30"/>
+      <c r="AO15" s="31"/>
       <c r="AP15" s="8"/>
       <c r="AQ15" s="8"/>
       <c r="AR15" s="9"/>
@@ -2541,58 +2541,58 @@
       <c r="A16" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
       <c r="H16" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="31" t="s">
+      <c r="I16" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
       <c r="O16" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="31" t="s">
+      <c r="P16" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="31"/>
-      <c r="T16" s="31"/>
-      <c r="U16" s="31"/>
-      <c r="V16" s="31"/>
-      <c r="W16" s="31"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="31"/>
-      <c r="Z16" s="144"/>
-      <c r="AA16" s="101"/>
-      <c r="AB16" s="30"/>
-      <c r="AC16" s="28"/>
-      <c r="AD16" s="28"/>
-      <c r="AE16" s="28"/>
-      <c r="AF16" s="28"/>
-      <c r="AG16" s="29"/>
-      <c r="AH16" s="33" t="s">
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="43"/>
+      <c r="AA16" s="41"/>
+      <c r="AB16" s="61"/>
+      <c r="AC16" s="56"/>
+      <c r="AD16" s="56"/>
+      <c r="AE16" s="56"/>
+      <c r="AF16" s="56"/>
+      <c r="AG16" s="57"/>
+      <c r="AH16" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="AI16" s="34"/>
-      <c r="AJ16" s="34"/>
-      <c r="AK16" s="34"/>
-      <c r="AL16" s="34"/>
-      <c r="AM16" s="34"/>
-      <c r="AN16" s="34"/>
-      <c r="AO16" s="35"/>
+      <c r="AI16" s="30"/>
+      <c r="AJ16" s="30"/>
+      <c r="AK16" s="30"/>
+      <c r="AL16" s="30"/>
+      <c r="AM16" s="30"/>
+      <c r="AN16" s="30"/>
+      <c r="AO16" s="31"/>
       <c r="AP16" s="8"/>
       <c r="AQ16" s="8"/>
       <c r="AR16" s="9"/>
@@ -2601,60 +2601,60 @@
       <c r="A17" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
       <c r="H17" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="31" t="s">
+      <c r="I17" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
       <c r="O17" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="P17" s="31" t="s">
+      <c r="P17" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="31"/>
-      <c r="S17" s="31"/>
-      <c r="T17" s="31"/>
-      <c r="U17" s="31"/>
-      <c r="V17" s="31"/>
-      <c r="W17" s="31"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="144"/>
-      <c r="AA17" s="101"/>
-      <c r="AB17" s="27" t="s">
+      <c r="Q17" s="27"/>
+      <c r="R17" s="27"/>
+      <c r="S17" s="27"/>
+      <c r="T17" s="27"/>
+      <c r="U17" s="27"/>
+      <c r="V17" s="27"/>
+      <c r="W17" s="27"/>
+      <c r="X17" s="27"/>
+      <c r="Y17" s="27"/>
+      <c r="Z17" s="43"/>
+      <c r="AA17" s="41"/>
+      <c r="AB17" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="AC17" s="28"/>
-      <c r="AD17" s="28"/>
-      <c r="AE17" s="28"/>
-      <c r="AF17" s="28"/>
-      <c r="AG17" s="29"/>
-      <c r="AH17" s="33" t="s">
+      <c r="AC17" s="56"/>
+      <c r="AD17" s="56"/>
+      <c r="AE17" s="56"/>
+      <c r="AF17" s="56"/>
+      <c r="AG17" s="57"/>
+      <c r="AH17" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="AI17" s="34"/>
-      <c r="AJ17" s="34"/>
-      <c r="AK17" s="34"/>
-      <c r="AL17" s="34"/>
-      <c r="AM17" s="34"/>
-      <c r="AN17" s="34"/>
-      <c r="AO17" s="35"/>
+      <c r="AI17" s="30"/>
+      <c r="AJ17" s="30"/>
+      <c r="AK17" s="30"/>
+      <c r="AL17" s="30"/>
+      <c r="AM17" s="30"/>
+      <c r="AN17" s="30"/>
+      <c r="AO17" s="31"/>
       <c r="AP17" s="8"/>
       <c r="AQ17" s="8"/>
       <c r="AR17" s="9"/>
@@ -2663,54 +2663,54 @@
       <c r="A18" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
       <c r="H18" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="I18" s="31" t="s">
+      <c r="I18" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
       <c r="N18" s="25"/>
       <c r="O18" s="26"/>
-      <c r="P18" s="31"/>
-      <c r="Q18" s="31"/>
-      <c r="R18" s="31"/>
-      <c r="S18" s="31"/>
-      <c r="T18" s="31"/>
-      <c r="U18" s="31"/>
-      <c r="V18" s="31"/>
-      <c r="W18" s="31"/>
-      <c r="X18" s="31"/>
-      <c r="Y18" s="31"/>
-      <c r="Z18" s="144"/>
-      <c r="AA18" s="101"/>
-      <c r="AB18" s="30"/>
-      <c r="AC18" s="28"/>
-      <c r="AD18" s="28"/>
-      <c r="AE18" s="28"/>
-      <c r="AF18" s="28"/>
-      <c r="AG18" s="29"/>
-      <c r="AH18" s="33" t="s">
+      <c r="P18" s="27"/>
+      <c r="Q18" s="27"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
+      <c r="U18" s="27"/>
+      <c r="V18" s="27"/>
+      <c r="W18" s="27"/>
+      <c r="X18" s="27"/>
+      <c r="Y18" s="27"/>
+      <c r="Z18" s="43"/>
+      <c r="AA18" s="41"/>
+      <c r="AB18" s="61"/>
+      <c r="AC18" s="56"/>
+      <c r="AD18" s="56"/>
+      <c r="AE18" s="56"/>
+      <c r="AF18" s="56"/>
+      <c r="AG18" s="57"/>
+      <c r="AH18" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="AI18" s="34"/>
-      <c r="AJ18" s="34"/>
-      <c r="AK18" s="34"/>
-      <c r="AL18" s="34"/>
-      <c r="AM18" s="34"/>
-      <c r="AN18" s="34"/>
-      <c r="AO18" s="35"/>
+      <c r="AI18" s="30"/>
+      <c r="AJ18" s="30"/>
+      <c r="AK18" s="30"/>
+      <c r="AL18" s="30"/>
+      <c r="AM18" s="30"/>
+      <c r="AN18" s="30"/>
+      <c r="AO18" s="31"/>
       <c r="AP18" s="8"/>
       <c r="AQ18" s="8"/>
       <c r="AR18" s="9"/>
@@ -2719,48 +2719,48 @@
       <c r="A19" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="40"/>
-      <c r="R19" s="40"/>
-      <c r="S19" s="40"/>
-      <c r="T19" s="40"/>
-      <c r="U19" s="40"/>
-      <c r="V19" s="40"/>
-      <c r="W19" s="40"/>
-      <c r="X19" s="40"/>
-      <c r="Y19" s="40"/>
-      <c r="Z19" s="41"/>
-      <c r="AA19" s="101"/>
-      <c r="AB19" s="30"/>
-      <c r="AC19" s="28"/>
-      <c r="AD19" s="28"/>
-      <c r="AE19" s="28"/>
-      <c r="AF19" s="28"/>
-      <c r="AG19" s="29"/>
-      <c r="AH19" s="33" t="s">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
+      <c r="S19" s="36"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="36"/>
+      <c r="V19" s="36"/>
+      <c r="W19" s="36"/>
+      <c r="X19" s="36"/>
+      <c r="Y19" s="36"/>
+      <c r="Z19" s="37"/>
+      <c r="AA19" s="41"/>
+      <c r="AB19" s="61"/>
+      <c r="AC19" s="56"/>
+      <c r="AD19" s="56"/>
+      <c r="AE19" s="56"/>
+      <c r="AF19" s="56"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="AI19" s="34"/>
-      <c r="AJ19" s="34"/>
-      <c r="AK19" s="34"/>
-      <c r="AL19" s="34"/>
-      <c r="AM19" s="34"/>
-      <c r="AN19" s="34"/>
-      <c r="AO19" s="35"/>
+      <c r="AI19" s="30"/>
+      <c r="AJ19" s="30"/>
+      <c r="AK19" s="30"/>
+      <c r="AL19" s="30"/>
+      <c r="AM19" s="30"/>
+      <c r="AN19" s="30"/>
+      <c r="AO19" s="31"/>
       <c r="AP19" s="8"/>
       <c r="AQ19" s="8"/>
       <c r="AR19" s="9"/>
@@ -2792,23 +2792,23 @@
       <c r="X20" s="4"/>
       <c r="Y20" s="4"/>
       <c r="Z20" s="5"/>
-      <c r="AA20" s="101"/>
-      <c r="AB20" s="30"/>
-      <c r="AC20" s="28"/>
-      <c r="AD20" s="28"/>
-      <c r="AE20" s="28"/>
-      <c r="AF20" s="28"/>
-      <c r="AG20" s="29"/>
-      <c r="AH20" s="33" t="s">
+      <c r="AA20" s="41"/>
+      <c r="AB20" s="61"/>
+      <c r="AC20" s="56"/>
+      <c r="AD20" s="56"/>
+      <c r="AE20" s="56"/>
+      <c r="AF20" s="56"/>
+      <c r="AG20" s="57"/>
+      <c r="AH20" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="AI20" s="34"/>
-      <c r="AJ20" s="34"/>
-      <c r="AK20" s="34"/>
-      <c r="AL20" s="34"/>
-      <c r="AM20" s="34"/>
-      <c r="AN20" s="34"/>
-      <c r="AO20" s="35"/>
+      <c r="AI20" s="30"/>
+      <c r="AJ20" s="30"/>
+      <c r="AK20" s="30"/>
+      <c r="AL20" s="30"/>
+      <c r="AM20" s="30"/>
+      <c r="AN20" s="30"/>
+      <c r="AO20" s="31"/>
       <c r="AP20" s="8"/>
       <c r="AQ20" s="8"/>
       <c r="AR20" s="9"/>
@@ -2822,12 +2822,12 @@
       <c r="D21" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
       <c r="I21" s="17" t="s">
         <v>23</v>
       </c>
@@ -2840,95 +2840,95 @@
       <c r="N21" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="O21" s="31" t="s">
+      <c r="O21" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="P21" s="31"/>
-      <c r="Q21" s="31"/>
-      <c r="R21" s="31"/>
-      <c r="S21" s="31"/>
+      <c r="P21" s="27"/>
+      <c r="Q21" s="27"/>
+      <c r="R21" s="27"/>
+      <c r="S21" s="27"/>
       <c r="T21" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U21" s="31" t="s">
+      <c r="U21" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="V21" s="31"/>
-      <c r="W21" s="31"/>
-      <c r="X21" s="31"/>
-      <c r="Y21" s="31"/>
-      <c r="Z21" s="144"/>
-      <c r="AA21" s="101"/>
-      <c r="AB21" s="30"/>
-      <c r="AC21" s="28"/>
-      <c r="AD21" s="28"/>
-      <c r="AE21" s="28"/>
-      <c r="AF21" s="28"/>
-      <c r="AG21" s="29"/>
-      <c r="AH21" s="33" t="s">
+      <c r="V21" s="27"/>
+      <c r="W21" s="27"/>
+      <c r="X21" s="27"/>
+      <c r="Y21" s="27"/>
+      <c r="Z21" s="43"/>
+      <c r="AA21" s="41"/>
+      <c r="AB21" s="61"/>
+      <c r="AC21" s="56"/>
+      <c r="AD21" s="56"/>
+      <c r="AE21" s="56"/>
+      <c r="AF21" s="56"/>
+      <c r="AG21" s="57"/>
+      <c r="AH21" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="AI21" s="34"/>
-      <c r="AJ21" s="34"/>
-      <c r="AK21" s="34"/>
-      <c r="AL21" s="34"/>
-      <c r="AM21" s="34"/>
-      <c r="AN21" s="34"/>
-      <c r="AO21" s="35"/>
+      <c r="AI21" s="30"/>
+      <c r="AJ21" s="30"/>
+      <c r="AK21" s="30"/>
+      <c r="AL21" s="30"/>
+      <c r="AM21" s="30"/>
+      <c r="AN21" s="30"/>
+      <c r="AO21" s="31"/>
       <c r="AP21" s="8"/>
       <c r="AQ21" s="8"/>
       <c r="AR21" s="9"/>
     </row>
     <row r="22" spans="1:44" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="89" t="s">
+      <c r="A22" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32"/>
-      <c r="O22" s="32"/>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="32"/>
-      <c r="R22" s="32"/>
-      <c r="S22" s="32"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
       <c r="T22" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U22" s="42" t="s">
+      <c r="U22" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="V22" s="32"/>
-      <c r="W22" s="32"/>
-      <c r="X22" s="32"/>
-      <c r="Y22" s="32"/>
-      <c r="Z22" s="43"/>
-      <c r="AA22" s="101"/>
-      <c r="AB22" s="30"/>
-      <c r="AC22" s="28"/>
-      <c r="AD22" s="28"/>
-      <c r="AE22" s="28"/>
-      <c r="AF22" s="28"/>
-      <c r="AG22" s="29"/>
-      <c r="AH22" s="33" t="s">
+      <c r="V22" s="28"/>
+      <c r="W22" s="28"/>
+      <c r="X22" s="28"/>
+      <c r="Y22" s="28"/>
+      <c r="Z22" s="39"/>
+      <c r="AA22" s="41"/>
+      <c r="AB22" s="61"/>
+      <c r="AC22" s="56"/>
+      <c r="AD22" s="56"/>
+      <c r="AE22" s="56"/>
+      <c r="AF22" s="56"/>
+      <c r="AG22" s="57"/>
+      <c r="AH22" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="AI22" s="34"/>
-      <c r="AJ22" s="34"/>
-      <c r="AK22" s="34"/>
-      <c r="AL22" s="34"/>
-      <c r="AM22" s="34"/>
-      <c r="AN22" s="34"/>
-      <c r="AO22" s="35"/>
+      <c r="AI22" s="30"/>
+      <c r="AJ22" s="30"/>
+      <c r="AK22" s="30"/>
+      <c r="AL22" s="30"/>
+      <c r="AM22" s="30"/>
+      <c r="AN22" s="30"/>
+      <c r="AO22" s="31"/>
       <c r="AP22" s="8"/>
       <c r="AQ22" s="8"/>
       <c r="AR22" s="9"/>
@@ -2946,51 +2946,51 @@
       <c r="H23" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="I23" s="31" t="s">
+      <c r="I23" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="O23" s="31" t="s">
+      <c r="O23" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="P23" s="32"/>
-      <c r="Q23" s="32"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
       <c r="T23" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U23" s="86" t="s">
+      <c r="U23" s="94" t="s">
         <v>87</v>
       </c>
-      <c r="V23" s="87"/>
-      <c r="W23" s="87"/>
-      <c r="X23" s="87"/>
-      <c r="Y23" s="87"/>
-      <c r="Z23" s="88"/>
-      <c r="AA23" s="101"/>
-      <c r="AB23" s="30"/>
-      <c r="AC23" s="28"/>
-      <c r="AD23" s="28"/>
-      <c r="AE23" s="28"/>
-      <c r="AF23" s="28"/>
-      <c r="AG23" s="29"/>
-      <c r="AH23" s="33" t="s">
+      <c r="V23" s="95"/>
+      <c r="W23" s="95"/>
+      <c r="X23" s="95"/>
+      <c r="Y23" s="95"/>
+      <c r="Z23" s="96"/>
+      <c r="AA23" s="41"/>
+      <c r="AB23" s="61"/>
+      <c r="AC23" s="56"/>
+      <c r="AD23" s="56"/>
+      <c r="AE23" s="56"/>
+      <c r="AF23" s="56"/>
+      <c r="AG23" s="57"/>
+      <c r="AH23" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="AI23" s="34"/>
-      <c r="AJ23" s="34"/>
-      <c r="AK23" s="34"/>
-      <c r="AL23" s="34"/>
-      <c r="AM23" s="34"/>
-      <c r="AN23" s="34"/>
-      <c r="AO23" s="35"/>
+      <c r="AI23" s="30"/>
+      <c r="AJ23" s="30"/>
+      <c r="AK23" s="30"/>
+      <c r="AL23" s="30"/>
+      <c r="AM23" s="30"/>
+      <c r="AN23" s="30"/>
+      <c r="AO23" s="31"/>
       <c r="AP23" s="8"/>
       <c r="AQ23" s="8"/>
       <c r="AR23" s="9"/>
@@ -2999,48 +2999,48 @@
       <c r="A24" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="40"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="40"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="40"/>
-      <c r="P24" s="40"/>
-      <c r="Q24" s="40"/>
-      <c r="R24" s="40"/>
-      <c r="S24" s="40"/>
-      <c r="T24" s="40"/>
-      <c r="U24" s="40"/>
-      <c r="V24" s="40"/>
-      <c r="W24" s="40"/>
-      <c r="X24" s="40"/>
-      <c r="Y24" s="40"/>
-      <c r="Z24" s="41"/>
-      <c r="AA24" s="101"/>
-      <c r="AB24" s="30"/>
-      <c r="AC24" s="28"/>
-      <c r="AD24" s="28"/>
-      <c r="AE24" s="28"/>
-      <c r="AF24" s="28"/>
-      <c r="AG24" s="29"/>
-      <c r="AH24" s="33" t="s">
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="36"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="36"/>
+      <c r="R24" s="36"/>
+      <c r="S24" s="36"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="36"/>
+      <c r="V24" s="36"/>
+      <c r="W24" s="36"/>
+      <c r="X24" s="36"/>
+      <c r="Y24" s="36"/>
+      <c r="Z24" s="37"/>
+      <c r="AA24" s="41"/>
+      <c r="AB24" s="61"/>
+      <c r="AC24" s="56"/>
+      <c r="AD24" s="56"/>
+      <c r="AE24" s="56"/>
+      <c r="AF24" s="56"/>
+      <c r="AG24" s="57"/>
+      <c r="AH24" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="AI24" s="34"/>
-      <c r="AJ24" s="34"/>
-      <c r="AK24" s="34"/>
-      <c r="AL24" s="34"/>
-      <c r="AM24" s="34"/>
-      <c r="AN24" s="34"/>
-      <c r="AO24" s="35"/>
+      <c r="AI24" s="30"/>
+      <c r="AJ24" s="30"/>
+      <c r="AK24" s="30"/>
+      <c r="AL24" s="30"/>
+      <c r="AM24" s="30"/>
+      <c r="AN24" s="30"/>
+      <c r="AO24" s="31"/>
       <c r="AP24" s="8"/>
       <c r="AQ24" s="8"/>
       <c r="AR24" s="9"/>
@@ -3072,789 +3072,789 @@
       <c r="X25" s="19"/>
       <c r="Y25" s="19"/>
       <c r="Z25" s="20"/>
-      <c r="AA25" s="101"/>
-      <c r="AB25" s="30"/>
-      <c r="AC25" s="28"/>
-      <c r="AD25" s="28"/>
-      <c r="AE25" s="28"/>
-      <c r="AF25" s="28"/>
-      <c r="AG25" s="29"/>
-      <c r="AH25" s="33" t="s">
+      <c r="AA25" s="41"/>
+      <c r="AB25" s="61"/>
+      <c r="AC25" s="56"/>
+      <c r="AD25" s="56"/>
+      <c r="AE25" s="56"/>
+      <c r="AF25" s="56"/>
+      <c r="AG25" s="57"/>
+      <c r="AH25" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="AI25" s="34"/>
-      <c r="AJ25" s="34"/>
-      <c r="AK25" s="34"/>
-      <c r="AL25" s="34"/>
-      <c r="AM25" s="34"/>
-      <c r="AN25" s="34"/>
-      <c r="AO25" s="35"/>
+      <c r="AI25" s="30"/>
+      <c r="AJ25" s="30"/>
+      <c r="AK25" s="30"/>
+      <c r="AL25" s="30"/>
+      <c r="AM25" s="30"/>
+      <c r="AN25" s="30"/>
+      <c r="AO25" s="31"/>
       <c r="AP25" s="8"/>
       <c r="AQ25" s="8"/>
       <c r="AR25" s="9"/>
     </row>
     <row r="26" spans="1:44" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="52" t="s">
+      <c r="A26" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="53"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="53"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="53"/>
-      <c r="P26" s="53"/>
-      <c r="Q26" s="53"/>
-      <c r="R26" s="53"/>
-      <c r="S26" s="53"/>
-      <c r="T26" s="53"/>
-      <c r="U26" s="53"/>
-      <c r="V26" s="53"/>
-      <c r="W26" s="53"/>
-      <c r="X26" s="53"/>
-      <c r="Y26" s="53"/>
-      <c r="Z26" s="54"/>
-      <c r="AA26" s="101"/>
-      <c r="AB26" s="30"/>
-      <c r="AC26" s="28"/>
-      <c r="AD26" s="28"/>
-      <c r="AE26" s="28"/>
-      <c r="AF26" s="28"/>
-      <c r="AG26" s="29"/>
-      <c r="AH26" s="33" t="s">
+      <c r="B26" s="63"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="63"/>
+      <c r="K26" s="63"/>
+      <c r="L26" s="63"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="63"/>
+      <c r="P26" s="63"/>
+      <c r="Q26" s="63"/>
+      <c r="R26" s="63"/>
+      <c r="S26" s="63"/>
+      <c r="T26" s="63"/>
+      <c r="U26" s="63"/>
+      <c r="V26" s="63"/>
+      <c r="W26" s="63"/>
+      <c r="X26" s="63"/>
+      <c r="Y26" s="63"/>
+      <c r="Z26" s="64"/>
+      <c r="AA26" s="41"/>
+      <c r="AB26" s="61"/>
+      <c r="AC26" s="56"/>
+      <c r="AD26" s="56"/>
+      <c r="AE26" s="56"/>
+      <c r="AF26" s="56"/>
+      <c r="AG26" s="57"/>
+      <c r="AH26" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="AI26" s="34"/>
-      <c r="AJ26" s="34"/>
-      <c r="AK26" s="34"/>
-      <c r="AL26" s="34"/>
-      <c r="AM26" s="34"/>
-      <c r="AN26" s="34"/>
-      <c r="AO26" s="35"/>
+      <c r="AI26" s="30"/>
+      <c r="AJ26" s="30"/>
+      <c r="AK26" s="30"/>
+      <c r="AL26" s="30"/>
+      <c r="AM26" s="30"/>
+      <c r="AN26" s="30"/>
+      <c r="AO26" s="31"/>
       <c r="AP26" s="8"/>
       <c r="AQ26" s="8"/>
       <c r="AR26" s="9"/>
     </row>
     <row r="27" spans="1:44" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="55"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="56"/>
-      <c r="M27" s="56"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="56"/>
-      <c r="P27" s="56"/>
-      <c r="Q27" s="56"/>
-      <c r="R27" s="56"/>
-      <c r="S27" s="56"/>
-      <c r="T27" s="56"/>
-      <c r="U27" s="56"/>
-      <c r="V27" s="56"/>
-      <c r="W27" s="56"/>
-      <c r="X27" s="56"/>
-      <c r="Y27" s="56"/>
-      <c r="Z27" s="57"/>
-      <c r="AA27" s="101"/>
-      <c r="AB27" s="30"/>
-      <c r="AC27" s="28"/>
-      <c r="AD27" s="28"/>
-      <c r="AE27" s="28"/>
-      <c r="AF27" s="28"/>
-      <c r="AG27" s="29"/>
-      <c r="AH27" s="33" t="s">
+      <c r="A27" s="65"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="66"/>
+      <c r="J27" s="66"/>
+      <c r="K27" s="66"/>
+      <c r="L27" s="66"/>
+      <c r="M27" s="66"/>
+      <c r="N27" s="66"/>
+      <c r="O27" s="66"/>
+      <c r="P27" s="66"/>
+      <c r="Q27" s="66"/>
+      <c r="R27" s="66"/>
+      <c r="S27" s="66"/>
+      <c r="T27" s="66"/>
+      <c r="U27" s="66"/>
+      <c r="V27" s="66"/>
+      <c r="W27" s="66"/>
+      <c r="X27" s="66"/>
+      <c r="Y27" s="66"/>
+      <c r="Z27" s="67"/>
+      <c r="AA27" s="41"/>
+      <c r="AB27" s="61"/>
+      <c r="AC27" s="56"/>
+      <c r="AD27" s="56"/>
+      <c r="AE27" s="56"/>
+      <c r="AF27" s="56"/>
+      <c r="AG27" s="57"/>
+      <c r="AH27" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="AI27" s="34"/>
-      <c r="AJ27" s="34"/>
-      <c r="AK27" s="34"/>
-      <c r="AL27" s="34"/>
-      <c r="AM27" s="34"/>
-      <c r="AN27" s="34"/>
-      <c r="AO27" s="35"/>
+      <c r="AI27" s="30"/>
+      <c r="AJ27" s="30"/>
+      <c r="AK27" s="30"/>
+      <c r="AL27" s="30"/>
+      <c r="AM27" s="30"/>
+      <c r="AN27" s="30"/>
+      <c r="AO27" s="31"/>
       <c r="AP27" s="8"/>
       <c r="AQ27" s="8"/>
       <c r="AR27" s="9"/>
     </row>
     <row r="28" spans="1:44" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="77" t="s">
+      <c r="A28" s="85" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="78"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="78"/>
-      <c r="E28" s="78"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="78"/>
-      <c r="H28" s="78"/>
-      <c r="I28" s="78"/>
-      <c r="J28" s="78"/>
-      <c r="K28" s="78"/>
-      <c r="L28" s="78"/>
-      <c r="M28" s="78"/>
-      <c r="N28" s="78"/>
-      <c r="O28" s="78"/>
-      <c r="P28" s="78"/>
-      <c r="Q28" s="78"/>
-      <c r="R28" s="78"/>
-      <c r="S28" s="78"/>
-      <c r="T28" s="78"/>
-      <c r="U28" s="78"/>
-      <c r="V28" s="78"/>
-      <c r="W28" s="78"/>
-      <c r="X28" s="78"/>
-      <c r="Y28" s="78"/>
-      <c r="Z28" s="79"/>
-      <c r="AA28" s="101"/>
-      <c r="AB28" s="27" t="s">
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="86"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="K28" s="86"/>
+      <c r="L28" s="86"/>
+      <c r="M28" s="86"/>
+      <c r="N28" s="86"/>
+      <c r="O28" s="86"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="86"/>
+      <c r="R28" s="86"/>
+      <c r="S28" s="86"/>
+      <c r="T28" s="86"/>
+      <c r="U28" s="86"/>
+      <c r="V28" s="86"/>
+      <c r="W28" s="86"/>
+      <c r="X28" s="86"/>
+      <c r="Y28" s="86"/>
+      <c r="Z28" s="87"/>
+      <c r="AA28" s="41"/>
+      <c r="AB28" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="AC28" s="28"/>
-      <c r="AD28" s="28"/>
-      <c r="AE28" s="28"/>
-      <c r="AF28" s="28"/>
-      <c r="AG28" s="29"/>
-      <c r="AH28" s="33" t="s">
+      <c r="AC28" s="56"/>
+      <c r="AD28" s="56"/>
+      <c r="AE28" s="56"/>
+      <c r="AF28" s="56"/>
+      <c r="AG28" s="57"/>
+      <c r="AH28" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="AI28" s="34"/>
-      <c r="AJ28" s="34"/>
-      <c r="AK28" s="34"/>
-      <c r="AL28" s="34"/>
-      <c r="AM28" s="34"/>
-      <c r="AN28" s="34"/>
-      <c r="AO28" s="35"/>
+      <c r="AI28" s="30"/>
+      <c r="AJ28" s="30"/>
+      <c r="AK28" s="30"/>
+      <c r="AL28" s="30"/>
+      <c r="AM28" s="30"/>
+      <c r="AN28" s="30"/>
+      <c r="AO28" s="31"/>
       <c r="AP28" s="8"/>
       <c r="AQ28" s="8"/>
       <c r="AR28" s="9"/>
     </row>
     <row r="29" spans="1:44" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A29" s="49" t="s">
+      <c r="A29" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
-      <c r="N29" s="32"/>
-      <c r="O29" s="32"/>
-      <c r="P29" s="32"/>
-      <c r="Q29" s="32"/>
-      <c r="R29" s="32"/>
-      <c r="S29" s="32"/>
-      <c r="T29" s="32"/>
-      <c r="U29" s="32"/>
-      <c r="V29" s="32"/>
-      <c r="W29" s="32"/>
-      <c r="X29" s="32"/>
-      <c r="Y29" s="32"/>
-      <c r="Z29" s="43"/>
-      <c r="AA29" s="101"/>
-      <c r="AB29" s="27" t="s">
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="28"/>
+      <c r="V29" s="28"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="28"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="39"/>
+      <c r="AA29" s="41"/>
+      <c r="AB29" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="AC29" s="28"/>
-      <c r="AD29" s="28"/>
-      <c r="AE29" s="28"/>
-      <c r="AF29" s="28"/>
-      <c r="AG29" s="29"/>
-      <c r="AH29" s="58" t="s">
+      <c r="AC29" s="56"/>
+      <c r="AD29" s="56"/>
+      <c r="AE29" s="56"/>
+      <c r="AF29" s="56"/>
+      <c r="AG29" s="57"/>
+      <c r="AH29" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="AI29" s="59"/>
-      <c r="AJ29" s="59"/>
-      <c r="AK29" s="59"/>
-      <c r="AL29" s="59"/>
-      <c r="AM29" s="59"/>
-      <c r="AN29" s="59"/>
-      <c r="AO29" s="60"/>
+      <c r="AI29" s="69"/>
+      <c r="AJ29" s="69"/>
+      <c r="AK29" s="69"/>
+      <c r="AL29" s="69"/>
+      <c r="AM29" s="69"/>
+      <c r="AN29" s="69"/>
+      <c r="AO29" s="70"/>
       <c r="AP29" s="8"/>
       <c r="AQ29" s="8"/>
       <c r="AR29" s="9"/>
     </row>
     <row r="30" spans="1:44" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="50"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="34"/>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="34"/>
-      <c r="R30" s="34"/>
-      <c r="S30" s="34"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="34"/>
-      <c r="V30" s="34"/>
-      <c r="W30" s="34"/>
-      <c r="X30" s="34"/>
-      <c r="Y30" s="34"/>
-      <c r="Z30" s="51"/>
-      <c r="AA30" s="101"/>
-      <c r="AB30" s="45" t="s">
+      <c r="A30" s="59"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="30"/>
+      <c r="Q30" s="30"/>
+      <c r="R30" s="30"/>
+      <c r="S30" s="30"/>
+      <c r="T30" s="30"/>
+      <c r="U30" s="30"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="30"/>
+      <c r="X30" s="30"/>
+      <c r="Y30" s="30"/>
+      <c r="Z30" s="60"/>
+      <c r="AA30" s="41"/>
+      <c r="AB30" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="AC30" s="46"/>
-      <c r="AD30" s="46"/>
-      <c r="AE30" s="46"/>
-      <c r="AF30" s="46"/>
-      <c r="AG30" s="46"/>
-      <c r="AH30" s="46"/>
-      <c r="AI30" s="46"/>
-      <c r="AJ30" s="46"/>
-      <c r="AK30" s="46"/>
-      <c r="AL30" s="46"/>
-      <c r="AM30" s="46"/>
-      <c r="AN30" s="46"/>
-      <c r="AO30" s="46"/>
-      <c r="AP30" s="46"/>
-      <c r="AQ30" s="46"/>
-      <c r="AR30" s="47"/>
+      <c r="AC30" s="52"/>
+      <c r="AD30" s="52"/>
+      <c r="AE30" s="52"/>
+      <c r="AF30" s="52"/>
+      <c r="AG30" s="52"/>
+      <c r="AH30" s="52"/>
+      <c r="AI30" s="52"/>
+      <c r="AJ30" s="52"/>
+      <c r="AK30" s="52"/>
+      <c r="AL30" s="52"/>
+      <c r="AM30" s="52"/>
+      <c r="AN30" s="52"/>
+      <c r="AO30" s="52"/>
+      <c r="AP30" s="52"/>
+      <c r="AQ30" s="52"/>
+      <c r="AR30" s="53"/>
     </row>
     <row r="31" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A31" s="61" t="s">
+      <c r="A31" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="B31" s="62"/>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="67" t="s">
+      <c r="B31" s="45"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="I31" s="62"/>
-      <c r="J31" s="62"/>
-      <c r="K31" s="62"/>
-      <c r="L31" s="62"/>
-      <c r="M31" s="62"/>
-      <c r="N31" s="63"/>
-      <c r="O31" s="67" t="s">
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="45"/>
+      <c r="M31" s="45"/>
+      <c r="N31" s="71"/>
+      <c r="O31" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="P31" s="62"/>
-      <c r="Q31" s="62"/>
-      <c r="R31" s="62"/>
-      <c r="S31" s="63"/>
-      <c r="T31" s="69" t="s">
+      <c r="P31" s="45"/>
+      <c r="Q31" s="45"/>
+      <c r="R31" s="45"/>
+      <c r="S31" s="71"/>
+      <c r="T31" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="U31" s="70"/>
-      <c r="V31" s="70"/>
-      <c r="W31" s="70"/>
-      <c r="X31" s="70"/>
-      <c r="Y31" s="70"/>
-      <c r="Z31" s="71"/>
-      <c r="AA31" s="101"/>
-      <c r="AB31" s="118" t="s">
+      <c r="U31" s="78"/>
+      <c r="V31" s="78"/>
+      <c r="W31" s="78"/>
+      <c r="X31" s="78"/>
+      <c r="Y31" s="78"/>
+      <c r="Z31" s="79"/>
+      <c r="AA31" s="41"/>
+      <c r="AB31" s="120" t="s">
         <v>63</v>
       </c>
-      <c r="AC31" s="119"/>
-      <c r="AD31" s="119"/>
-      <c r="AE31" s="119"/>
-      <c r="AF31" s="119"/>
-      <c r="AG31" s="119"/>
-      <c r="AH31" s="119"/>
-      <c r="AI31" s="119"/>
-      <c r="AJ31" s="119"/>
-      <c r="AK31" s="119"/>
-      <c r="AL31" s="119"/>
-      <c r="AM31" s="119"/>
-      <c r="AN31" s="119"/>
-      <c r="AO31" s="119"/>
-      <c r="AP31" s="119"/>
-      <c r="AQ31" s="119"/>
-      <c r="AR31" s="120"/>
+      <c r="AC31" s="121"/>
+      <c r="AD31" s="121"/>
+      <c r="AE31" s="121"/>
+      <c r="AF31" s="121"/>
+      <c r="AG31" s="121"/>
+      <c r="AH31" s="121"/>
+      <c r="AI31" s="121"/>
+      <c r="AJ31" s="121"/>
+      <c r="AK31" s="121"/>
+      <c r="AL31" s="121"/>
+      <c r="AM31" s="121"/>
+      <c r="AN31" s="121"/>
+      <c r="AO31" s="121"/>
+      <c r="AP31" s="121"/>
+      <c r="AQ31" s="121"/>
+      <c r="AR31" s="122"/>
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A32" s="64"/>
-      <c r="B32" s="65"/>
-      <c r="C32" s="65"/>
-      <c r="D32" s="65"/>
-      <c r="E32" s="65"/>
-      <c r="F32" s="65"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="68"/>
-      <c r="I32" s="65"/>
-      <c r="J32" s="65"/>
-      <c r="K32" s="65"/>
-      <c r="L32" s="65"/>
-      <c r="M32" s="65"/>
-      <c r="N32" s="66"/>
-      <c r="O32" s="68"/>
-      <c r="P32" s="65"/>
-      <c r="Q32" s="65"/>
-      <c r="R32" s="65"/>
-      <c r="S32" s="66"/>
-      <c r="T32" s="72"/>
-      <c r="U32" s="73"/>
-      <c r="V32" s="73"/>
-      <c r="W32" s="73"/>
-      <c r="X32" s="73"/>
-      <c r="Y32" s="73"/>
-      <c r="Z32" s="74"/>
-      <c r="AA32" s="101"/>
-      <c r="AB32" s="121"/>
-      <c r="AC32" s="122"/>
-      <c r="AD32" s="122"/>
-      <c r="AE32" s="122"/>
-      <c r="AF32" s="122"/>
-      <c r="AG32" s="122"/>
-      <c r="AH32" s="122"/>
-      <c r="AI32" s="122"/>
-      <c r="AJ32" s="122"/>
-      <c r="AK32" s="122"/>
-      <c r="AL32" s="122"/>
-      <c r="AM32" s="122"/>
-      <c r="AN32" s="122"/>
-      <c r="AO32" s="122"/>
-      <c r="AP32" s="122"/>
-      <c r="AQ32" s="122"/>
-      <c r="AR32" s="123"/>
+      <c r="A32" s="72"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="74"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="73"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="76"/>
+      <c r="P32" s="73"/>
+      <c r="Q32" s="73"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="74"/>
+      <c r="T32" s="80"/>
+      <c r="U32" s="81"/>
+      <c r="V32" s="81"/>
+      <c r="W32" s="81"/>
+      <c r="X32" s="81"/>
+      <c r="Y32" s="81"/>
+      <c r="Z32" s="82"/>
+      <c r="AA32" s="41"/>
+      <c r="AB32" s="123"/>
+      <c r="AC32" s="124"/>
+      <c r="AD32" s="124"/>
+      <c r="AE32" s="124"/>
+      <c r="AF32" s="124"/>
+      <c r="AG32" s="124"/>
+      <c r="AH32" s="124"/>
+      <c r="AI32" s="124"/>
+      <c r="AJ32" s="124"/>
+      <c r="AK32" s="124"/>
+      <c r="AL32" s="124"/>
+      <c r="AM32" s="124"/>
+      <c r="AN32" s="124"/>
+      <c r="AO32" s="124"/>
+      <c r="AP32" s="124"/>
+      <c r="AQ32" s="124"/>
+      <c r="AR32" s="125"/>
     </row>
     <row r="33" spans="1:44" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="97"/>
-      <c r="B33" s="98"/>
-      <c r="C33" s="98"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="98"/>
-      <c r="F33" s="98"/>
-      <c r="G33" s="98"/>
-      <c r="H33" s="98"/>
-      <c r="I33" s="98"/>
-      <c r="J33" s="98"/>
-      <c r="K33" s="98"/>
-      <c r="L33" s="98"/>
-      <c r="M33" s="98"/>
-      <c r="N33" s="98"/>
-      <c r="O33" s="98"/>
-      <c r="P33" s="98"/>
-      <c r="Q33" s="98"/>
-      <c r="R33" s="98"/>
-      <c r="S33" s="98"/>
-      <c r="T33" s="98"/>
-      <c r="U33" s="98"/>
-      <c r="V33" s="98"/>
-      <c r="W33" s="98"/>
-      <c r="X33" s="98"/>
-      <c r="Y33" s="98"/>
-      <c r="Z33" s="99"/>
-      <c r="AA33" s="101"/>
-      <c r="AB33" s="105" t="s">
+      <c r="A33" s="47"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="48"/>
+      <c r="M33" s="48"/>
+      <c r="N33" s="48"/>
+      <c r="O33" s="48"/>
+      <c r="P33" s="48"/>
+      <c r="Q33" s="48"/>
+      <c r="R33" s="48"/>
+      <c r="S33" s="48"/>
+      <c r="T33" s="48"/>
+      <c r="U33" s="48"/>
+      <c r="V33" s="48"/>
+      <c r="W33" s="48"/>
+      <c r="X33" s="48"/>
+      <c r="Y33" s="48"/>
+      <c r="Z33" s="49"/>
+      <c r="AA33" s="41"/>
+      <c r="AB33" s="107" t="s">
         <v>64</v>
       </c>
-      <c r="AC33" s="106"/>
-      <c r="AD33" s="106"/>
-      <c r="AE33" s="106"/>
-      <c r="AF33" s="106"/>
-      <c r="AG33" s="106"/>
-      <c r="AH33" s="106"/>
-      <c r="AI33" s="106"/>
-      <c r="AJ33" s="106"/>
-      <c r="AK33" s="106"/>
-      <c r="AL33" s="106"/>
-      <c r="AM33" s="106"/>
-      <c r="AN33" s="106"/>
-      <c r="AO33" s="106"/>
-      <c r="AP33" s="106"/>
-      <c r="AQ33" s="106"/>
-      <c r="AR33" s="107"/>
+      <c r="AC33" s="108"/>
+      <c r="AD33" s="108"/>
+      <c r="AE33" s="108"/>
+      <c r="AF33" s="108"/>
+      <c r="AG33" s="108"/>
+      <c r="AH33" s="108"/>
+      <c r="AI33" s="108"/>
+      <c r="AJ33" s="108"/>
+      <c r="AK33" s="108"/>
+      <c r="AL33" s="108"/>
+      <c r="AM33" s="108"/>
+      <c r="AN33" s="108"/>
+      <c r="AO33" s="108"/>
+      <c r="AP33" s="108"/>
+      <c r="AQ33" s="108"/>
+      <c r="AR33" s="109"/>
     </row>
     <row r="34" spans="1:44" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="97"/>
-      <c r="B34" s="98"/>
-      <c r="C34" s="98"/>
-      <c r="D34" s="98"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="98"/>
-      <c r="G34" s="98"/>
-      <c r="H34" s="98"/>
-      <c r="I34" s="98"/>
-      <c r="J34" s="98"/>
-      <c r="K34" s="98"/>
-      <c r="L34" s="98"/>
-      <c r="M34" s="98"/>
-      <c r="N34" s="98"/>
-      <c r="O34" s="98"/>
-      <c r="P34" s="98"/>
-      <c r="Q34" s="98"/>
-      <c r="R34" s="98"/>
-      <c r="S34" s="98"/>
-      <c r="T34" s="98"/>
-      <c r="U34" s="98"/>
-      <c r="V34" s="98"/>
-      <c r="W34" s="98"/>
-      <c r="X34" s="98"/>
-      <c r="Y34" s="98"/>
-      <c r="Z34" s="99"/>
-      <c r="AA34" s="101"/>
-      <c r="AB34" s="108"/>
-      <c r="AC34" s="109"/>
-      <c r="AD34" s="109"/>
-      <c r="AE34" s="109"/>
-      <c r="AF34" s="109"/>
-      <c r="AG34" s="109"/>
-      <c r="AH34" s="109"/>
-      <c r="AI34" s="109"/>
-      <c r="AJ34" s="109"/>
-      <c r="AK34" s="109"/>
-      <c r="AL34" s="109"/>
-      <c r="AM34" s="109"/>
-      <c r="AN34" s="109"/>
-      <c r="AO34" s="109"/>
-      <c r="AP34" s="109"/>
-      <c r="AQ34" s="109"/>
-      <c r="AR34" s="110"/>
+      <c r="A34" s="47"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="48"/>
+      <c r="J34" s="48"/>
+      <c r="K34" s="48"/>
+      <c r="L34" s="48"/>
+      <c r="M34" s="48"/>
+      <c r="N34" s="48"/>
+      <c r="O34" s="48"/>
+      <c r="P34" s="48"/>
+      <c r="Q34" s="48"/>
+      <c r="R34" s="48"/>
+      <c r="S34" s="48"/>
+      <c r="T34" s="48"/>
+      <c r="U34" s="48"/>
+      <c r="V34" s="48"/>
+      <c r="W34" s="48"/>
+      <c r="X34" s="48"/>
+      <c r="Y34" s="48"/>
+      <c r="Z34" s="49"/>
+      <c r="AA34" s="41"/>
+      <c r="AB34" s="110"/>
+      <c r="AC34" s="111"/>
+      <c r="AD34" s="111"/>
+      <c r="AE34" s="111"/>
+      <c r="AF34" s="111"/>
+      <c r="AG34" s="111"/>
+      <c r="AH34" s="111"/>
+      <c r="AI34" s="111"/>
+      <c r="AJ34" s="111"/>
+      <c r="AK34" s="111"/>
+      <c r="AL34" s="111"/>
+      <c r="AM34" s="111"/>
+      <c r="AN34" s="111"/>
+      <c r="AO34" s="111"/>
+      <c r="AP34" s="111"/>
+      <c r="AQ34" s="111"/>
+      <c r="AR34" s="112"/>
     </row>
     <row r="35" spans="1:44" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="97"/>
-      <c r="B35" s="98"/>
-      <c r="C35" s="98"/>
-      <c r="D35" s="98"/>
-      <c r="E35" s="98"/>
-      <c r="F35" s="98"/>
-      <c r="G35" s="98"/>
-      <c r="H35" s="98"/>
-      <c r="I35" s="98"/>
-      <c r="J35" s="98"/>
-      <c r="K35" s="98"/>
-      <c r="L35" s="98"/>
-      <c r="M35" s="98"/>
-      <c r="N35" s="98"/>
-      <c r="O35" s="98"/>
-      <c r="P35" s="98"/>
-      <c r="Q35" s="98"/>
-      <c r="R35" s="98"/>
-      <c r="S35" s="98"/>
-      <c r="T35" s="98"/>
-      <c r="U35" s="98"/>
-      <c r="V35" s="98"/>
-      <c r="W35" s="98"/>
-      <c r="X35" s="98"/>
-      <c r="Y35" s="98"/>
-      <c r="Z35" s="99"/>
-      <c r="AA35" s="101"/>
-      <c r="AB35" s="111" t="s">
+      <c r="A35" s="47"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="48"/>
+      <c r="J35" s="48"/>
+      <c r="K35" s="48"/>
+      <c r="L35" s="48"/>
+      <c r="M35" s="48"/>
+      <c r="N35" s="48"/>
+      <c r="O35" s="48"/>
+      <c r="P35" s="48"/>
+      <c r="Q35" s="48"/>
+      <c r="R35" s="48"/>
+      <c r="S35" s="48"/>
+      <c r="T35" s="48"/>
+      <c r="U35" s="48"/>
+      <c r="V35" s="48"/>
+      <c r="W35" s="48"/>
+      <c r="X35" s="48"/>
+      <c r="Y35" s="48"/>
+      <c r="Z35" s="49"/>
+      <c r="AA35" s="41"/>
+      <c r="AB35" s="113" t="s">
         <v>84</v>
       </c>
-      <c r="AC35" s="112"/>
-      <c r="AD35" s="112"/>
-      <c r="AE35" s="112"/>
-      <c r="AF35" s="112"/>
-      <c r="AG35" s="112"/>
-      <c r="AH35" s="112"/>
-      <c r="AI35" s="112"/>
-      <c r="AJ35" s="112"/>
-      <c r="AK35" s="112"/>
-      <c r="AL35" s="112"/>
-      <c r="AM35" s="112"/>
-      <c r="AN35" s="112"/>
-      <c r="AO35" s="114" t="s">
+      <c r="AC35" s="114"/>
+      <c r="AD35" s="114"/>
+      <c r="AE35" s="114"/>
+      <c r="AF35" s="114"/>
+      <c r="AG35" s="114"/>
+      <c r="AH35" s="114"/>
+      <c r="AI35" s="114"/>
+      <c r="AJ35" s="114"/>
+      <c r="AK35" s="114"/>
+      <c r="AL35" s="114"/>
+      <c r="AM35" s="114"/>
+      <c r="AN35" s="114"/>
+      <c r="AO35" s="116" t="s">
         <v>83</v>
       </c>
-      <c r="AP35" s="112"/>
-      <c r="AQ35" s="112"/>
-      <c r="AR35" s="116"/>
+      <c r="AP35" s="114"/>
+      <c r="AQ35" s="114"/>
+      <c r="AR35" s="118"/>
     </row>
     <row r="36" spans="1:44" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="97"/>
-      <c r="B36" s="98"/>
-      <c r="C36" s="98"/>
-      <c r="D36" s="98"/>
-      <c r="E36" s="98"/>
-      <c r="F36" s="98"/>
-      <c r="G36" s="98"/>
-      <c r="H36" s="98"/>
-      <c r="I36" s="98"/>
-      <c r="J36" s="98"/>
-      <c r="K36" s="98"/>
-      <c r="L36" s="98"/>
-      <c r="M36" s="98"/>
-      <c r="N36" s="98"/>
-      <c r="O36" s="98"/>
-      <c r="P36" s="98"/>
-      <c r="Q36" s="98"/>
-      <c r="R36" s="98"/>
-      <c r="S36" s="98"/>
-      <c r="T36" s="98"/>
-      <c r="U36" s="98"/>
-      <c r="V36" s="98"/>
-      <c r="W36" s="98"/>
-      <c r="X36" s="98"/>
-      <c r="Y36" s="98"/>
-      <c r="Z36" s="99"/>
-      <c r="AA36" s="101"/>
-      <c r="AB36" s="64"/>
-      <c r="AC36" s="113"/>
-      <c r="AD36" s="113"/>
-      <c r="AE36" s="113"/>
-      <c r="AF36" s="113"/>
-      <c r="AG36" s="113"/>
-      <c r="AH36" s="113"/>
-      <c r="AI36" s="113"/>
-      <c r="AJ36" s="113"/>
-      <c r="AK36" s="113"/>
-      <c r="AL36" s="113"/>
-      <c r="AM36" s="113"/>
-      <c r="AN36" s="113"/>
-      <c r="AO36" s="115"/>
-      <c r="AP36" s="113"/>
-      <c r="AQ36" s="113"/>
-      <c r="AR36" s="117"/>
+      <c r="A36" s="47"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
+      <c r="J36" s="48"/>
+      <c r="K36" s="48"/>
+      <c r="L36" s="48"/>
+      <c r="M36" s="48"/>
+      <c r="N36" s="48"/>
+      <c r="O36" s="48"/>
+      <c r="P36" s="48"/>
+      <c r="Q36" s="48"/>
+      <c r="R36" s="48"/>
+      <c r="S36" s="48"/>
+      <c r="T36" s="48"/>
+      <c r="U36" s="48"/>
+      <c r="V36" s="48"/>
+      <c r="W36" s="48"/>
+      <c r="X36" s="48"/>
+      <c r="Y36" s="48"/>
+      <c r="Z36" s="49"/>
+      <c r="AA36" s="41"/>
+      <c r="AB36" s="72"/>
+      <c r="AC36" s="115"/>
+      <c r="AD36" s="115"/>
+      <c r="AE36" s="115"/>
+      <c r="AF36" s="115"/>
+      <c r="AG36" s="115"/>
+      <c r="AH36" s="115"/>
+      <c r="AI36" s="115"/>
+      <c r="AJ36" s="115"/>
+      <c r="AK36" s="115"/>
+      <c r="AL36" s="115"/>
+      <c r="AM36" s="115"/>
+      <c r="AN36" s="115"/>
+      <c r="AO36" s="117"/>
+      <c r="AP36" s="115"/>
+      <c r="AQ36" s="115"/>
+      <c r="AR36" s="119"/>
     </row>
     <row r="37" spans="1:44" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="97"/>
-      <c r="B37" s="98"/>
-      <c r="C37" s="98"/>
-      <c r="D37" s="98"/>
-      <c r="E37" s="98"/>
-      <c r="F37" s="98"/>
-      <c r="G37" s="98"/>
-      <c r="H37" s="98"/>
-      <c r="I37" s="98"/>
-      <c r="J37" s="98"/>
-      <c r="K37" s="98"/>
-      <c r="L37" s="98"/>
-      <c r="M37" s="98"/>
-      <c r="N37" s="98"/>
-      <c r="O37" s="98"/>
-      <c r="P37" s="98"/>
-      <c r="Q37" s="98"/>
-      <c r="R37" s="98"/>
-      <c r="S37" s="98"/>
-      <c r="T37" s="98"/>
-      <c r="U37" s="98"/>
-      <c r="V37" s="98"/>
-      <c r="W37" s="98"/>
-      <c r="X37" s="98"/>
-      <c r="Y37" s="98"/>
-      <c r="Z37" s="99"/>
-      <c r="AA37" s="101"/>
+      <c r="A37" s="47"/>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="48"/>
+      <c r="R37" s="48"/>
+      <c r="S37" s="48"/>
+      <c r="T37" s="48"/>
+      <c r="U37" s="48"/>
+      <c r="V37" s="48"/>
+      <c r="W37" s="48"/>
+      <c r="X37" s="48"/>
+      <c r="Y37" s="48"/>
+      <c r="Z37" s="49"/>
+      <c r="AA37" s="41"/>
       <c r="AB37" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="AC37" s="40"/>
-      <c r="AD37" s="40"/>
-      <c r="AE37" s="40"/>
-      <c r="AF37" s="40"/>
-      <c r="AG37" s="40"/>
-      <c r="AH37" s="40"/>
-      <c r="AI37" s="40"/>
-      <c r="AJ37" s="40"/>
-      <c r="AK37" s="40"/>
-      <c r="AL37" s="40"/>
-      <c r="AM37" s="40"/>
-      <c r="AN37" s="40"/>
+      <c r="AC37" s="36"/>
+      <c r="AD37" s="36"/>
+      <c r="AE37" s="36"/>
+      <c r="AF37" s="36"/>
+      <c r="AG37" s="36"/>
+      <c r="AH37" s="36"/>
+      <c r="AI37" s="36"/>
+      <c r="AJ37" s="36"/>
+      <c r="AK37" s="36"/>
+      <c r="AL37" s="36"/>
+      <c r="AM37" s="36"/>
+      <c r="AN37" s="36"/>
       <c r="AO37" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="AP37" s="40"/>
-      <c r="AQ37" s="40"/>
-      <c r="AR37" s="41"/>
+      <c r="AP37" s="36"/>
+      <c r="AQ37" s="36"/>
+      <c r="AR37" s="37"/>
     </row>
     <row r="38" spans="1:44" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="97"/>
-      <c r="B38" s="98"/>
-      <c r="C38" s="98"/>
-      <c r="D38" s="98"/>
-      <c r="E38" s="98"/>
-      <c r="F38" s="98"/>
-      <c r="G38" s="98"/>
-      <c r="H38" s="98"/>
-      <c r="I38" s="98"/>
-      <c r="J38" s="98"/>
-      <c r="K38" s="98"/>
-      <c r="L38" s="98"/>
-      <c r="M38" s="98"/>
-      <c r="N38" s="98"/>
-      <c r="O38" s="98"/>
-      <c r="P38" s="98"/>
-      <c r="Q38" s="98"/>
-      <c r="R38" s="98"/>
-      <c r="S38" s="98"/>
-      <c r="T38" s="98"/>
-      <c r="U38" s="98"/>
-      <c r="V38" s="98"/>
-      <c r="W38" s="98"/>
-      <c r="X38" s="98"/>
-      <c r="Y38" s="98"/>
-      <c r="Z38" s="99"/>
-      <c r="AA38" s="101"/>
+      <c r="A38" s="47"/>
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="48"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="48"/>
+      <c r="I38" s="48"/>
+      <c r="J38" s="48"/>
+      <c r="K38" s="48"/>
+      <c r="L38" s="48"/>
+      <c r="M38" s="48"/>
+      <c r="N38" s="48"/>
+      <c r="O38" s="48"/>
+      <c r="P38" s="48"/>
+      <c r="Q38" s="48"/>
+      <c r="R38" s="48"/>
+      <c r="S38" s="48"/>
+      <c r="T38" s="48"/>
+      <c r="U38" s="48"/>
+      <c r="V38" s="48"/>
+      <c r="W38" s="48"/>
+      <c r="X38" s="48"/>
+      <c r="Y38" s="48"/>
+      <c r="Z38" s="49"/>
+      <c r="AA38" s="41"/>
       <c r="AB38" s="157" t="s">
         <v>68</v>
       </c>
-      <c r="AC38" s="40"/>
-      <c r="AD38" s="40"/>
-      <c r="AE38" s="40"/>
-      <c r="AF38" s="40"/>
-      <c r="AG38" s="40"/>
-      <c r="AH38" s="40"/>
-      <c r="AI38" s="40"/>
-      <c r="AJ38" s="40"/>
-      <c r="AK38" s="40"/>
-      <c r="AL38" s="40"/>
-      <c r="AM38" s="40"/>
-      <c r="AN38" s="40"/>
-      <c r="AO38" s="40"/>
-      <c r="AP38" s="40"/>
-      <c r="AQ38" s="40"/>
-      <c r="AR38" s="41"/>
+      <c r="AC38" s="36"/>
+      <c r="AD38" s="36"/>
+      <c r="AE38" s="36"/>
+      <c r="AF38" s="36"/>
+      <c r="AG38" s="36"/>
+      <c r="AH38" s="36"/>
+      <c r="AI38" s="36"/>
+      <c r="AJ38" s="36"/>
+      <c r="AK38" s="36"/>
+      <c r="AL38" s="36"/>
+      <c r="AM38" s="36"/>
+      <c r="AN38" s="36"/>
+      <c r="AO38" s="36"/>
+      <c r="AP38" s="36"/>
+      <c r="AQ38" s="36"/>
+      <c r="AR38" s="37"/>
     </row>
     <row r="39" spans="1:44" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="97"/>
-      <c r="B39" s="98"/>
-      <c r="C39" s="98"/>
-      <c r="D39" s="98"/>
-      <c r="E39" s="98"/>
-      <c r="F39" s="98"/>
-      <c r="G39" s="98"/>
-      <c r="H39" s="98"/>
-      <c r="I39" s="98"/>
-      <c r="J39" s="98"/>
-      <c r="K39" s="98"/>
-      <c r="L39" s="98"/>
-      <c r="M39" s="98"/>
-      <c r="N39" s="98"/>
-      <c r="O39" s="98"/>
-      <c r="P39" s="98"/>
-      <c r="Q39" s="98"/>
-      <c r="R39" s="98"/>
-      <c r="S39" s="98"/>
-      <c r="T39" s="98"/>
-      <c r="U39" s="98"/>
-      <c r="V39" s="98"/>
-      <c r="W39" s="98"/>
-      <c r="X39" s="98"/>
-      <c r="Y39" s="98"/>
-      <c r="Z39" s="99"/>
-      <c r="AA39" s="101"/>
+      <c r="A39" s="47"/>
+      <c r="B39" s="48"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="48"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="48"/>
+      <c r="J39" s="48"/>
+      <c r="K39" s="48"/>
+      <c r="L39" s="48"/>
+      <c r="M39" s="48"/>
+      <c r="N39" s="48"/>
+      <c r="O39" s="48"/>
+      <c r="P39" s="48"/>
+      <c r="Q39" s="48"/>
+      <c r="R39" s="48"/>
+      <c r="S39" s="48"/>
+      <c r="T39" s="48"/>
+      <c r="U39" s="48"/>
+      <c r="V39" s="48"/>
+      <c r="W39" s="48"/>
+      <c r="X39" s="48"/>
+      <c r="Y39" s="48"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="41"/>
       <c r="AB39" s="157"/>
-      <c r="AC39" s="40"/>
-      <c r="AD39" s="40"/>
-      <c r="AE39" s="40"/>
-      <c r="AF39" s="40"/>
-      <c r="AG39" s="40"/>
-      <c r="AH39" s="40"/>
-      <c r="AI39" s="40"/>
-      <c r="AJ39" s="40"/>
-      <c r="AK39" s="40"/>
-      <c r="AL39" s="40"/>
-      <c r="AM39" s="40"/>
-      <c r="AN39" s="40"/>
-      <c r="AO39" s="40"/>
-      <c r="AP39" s="40"/>
-      <c r="AQ39" s="40"/>
-      <c r="AR39" s="41"/>
+      <c r="AC39" s="36"/>
+      <c r="AD39" s="36"/>
+      <c r="AE39" s="36"/>
+      <c r="AF39" s="36"/>
+      <c r="AG39" s="36"/>
+      <c r="AH39" s="36"/>
+      <c r="AI39" s="36"/>
+      <c r="AJ39" s="36"/>
+      <c r="AK39" s="36"/>
+      <c r="AL39" s="36"/>
+      <c r="AM39" s="36"/>
+      <c r="AN39" s="36"/>
+      <c r="AO39" s="36"/>
+      <c r="AP39" s="36"/>
+      <c r="AQ39" s="36"/>
+      <c r="AR39" s="37"/>
     </row>
     <row r="40" spans="1:44" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="97"/>
-      <c r="B40" s="98"/>
-      <c r="C40" s="98"/>
-      <c r="D40" s="98"/>
-      <c r="E40" s="98"/>
-      <c r="F40" s="98"/>
-      <c r="G40" s="98"/>
-      <c r="H40" s="98"/>
-      <c r="I40" s="98"/>
-      <c r="J40" s="98"/>
-      <c r="K40" s="98"/>
-      <c r="L40" s="98"/>
-      <c r="M40" s="98"/>
-      <c r="N40" s="98"/>
-      <c r="O40" s="98"/>
-      <c r="P40" s="98"/>
-      <c r="Q40" s="98"/>
-      <c r="R40" s="98"/>
-      <c r="S40" s="98"/>
-      <c r="T40" s="98"/>
-      <c r="U40" s="98"/>
-      <c r="V40" s="98"/>
-      <c r="W40" s="98"/>
-      <c r="X40" s="98"/>
-      <c r="Y40" s="98"/>
-      <c r="Z40" s="99"/>
-      <c r="AA40" s="101"/>
+      <c r="A40" s="47"/>
+      <c r="B40" s="48"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48"/>
+      <c r="J40" s="48"/>
+      <c r="K40" s="48"/>
+      <c r="L40" s="48"/>
+      <c r="M40" s="48"/>
+      <c r="N40" s="48"/>
+      <c r="O40" s="48"/>
+      <c r="P40" s="48"/>
+      <c r="Q40" s="48"/>
+      <c r="R40" s="48"/>
+      <c r="S40" s="48"/>
+      <c r="T40" s="48"/>
+      <c r="U40" s="48"/>
+      <c r="V40" s="48"/>
+      <c r="W40" s="48"/>
+      <c r="X40" s="48"/>
+      <c r="Y40" s="48"/>
+      <c r="Z40" s="49"/>
+      <c r="AA40" s="41"/>
       <c r="AB40" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="AC40" s="92"/>
-      <c r="AD40" s="92"/>
-      <c r="AE40" s="92"/>
-      <c r="AF40" s="92"/>
-      <c r="AG40" s="92"/>
-      <c r="AH40" s="92"/>
-      <c r="AI40" s="92"/>
-      <c r="AJ40" s="92"/>
-      <c r="AK40" s="92"/>
-      <c r="AL40" s="75"/>
-      <c r="AM40" s="75"/>
-      <c r="AN40" s="75"/>
-      <c r="AO40" s="75"/>
-      <c r="AP40" s="75"/>
-      <c r="AQ40" s="75"/>
-      <c r="AR40" s="76"/>
+      <c r="AC40" s="100"/>
+      <c r="AD40" s="100"/>
+      <c r="AE40" s="100"/>
+      <c r="AF40" s="100"/>
+      <c r="AG40" s="100"/>
+      <c r="AH40" s="100"/>
+      <c r="AI40" s="100"/>
+      <c r="AJ40" s="100"/>
+      <c r="AK40" s="100"/>
+      <c r="AL40" s="83"/>
+      <c r="AM40" s="83"/>
+      <c r="AN40" s="83"/>
+      <c r="AO40" s="83"/>
+      <c r="AP40" s="83"/>
+      <c r="AQ40" s="83"/>
+      <c r="AR40" s="84"/>
     </row>
     <row r="41" spans="1:44" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="97"/>
-      <c r="B41" s="98"/>
-      <c r="C41" s="98"/>
-      <c r="D41" s="98"/>
-      <c r="E41" s="98"/>
-      <c r="F41" s="98"/>
-      <c r="G41" s="98"/>
-      <c r="H41" s="98"/>
-      <c r="I41" s="98"/>
-      <c r="J41" s="98"/>
-      <c r="K41" s="98"/>
-      <c r="L41" s="98"/>
-      <c r="M41" s="98"/>
-      <c r="N41" s="98"/>
-      <c r="O41" s="98"/>
-      <c r="P41" s="98"/>
-      <c r="Q41" s="98"/>
-      <c r="R41" s="98"/>
-      <c r="S41" s="98"/>
-      <c r="T41" s="98"/>
-      <c r="U41" s="98"/>
-      <c r="V41" s="98"/>
-      <c r="W41" s="98"/>
-      <c r="X41" s="98"/>
-      <c r="Y41" s="98"/>
-      <c r="Z41" s="99"/>
-      <c r="AA41" s="101"/>
+      <c r="A41" s="47"/>
+      <c r="B41" s="48"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="48"/>
+      <c r="J41" s="48"/>
+      <c r="K41" s="48"/>
+      <c r="L41" s="48"/>
+      <c r="M41" s="48"/>
+      <c r="N41" s="48"/>
+      <c r="O41" s="48"/>
+      <c r="P41" s="48"/>
+      <c r="Q41" s="48"/>
+      <c r="R41" s="48"/>
+      <c r="S41" s="48"/>
+      <c r="T41" s="48"/>
+      <c r="U41" s="48"/>
+      <c r="V41" s="48"/>
+      <c r="W41" s="48"/>
+      <c r="X41" s="48"/>
+      <c r="Y41" s="48"/>
+      <c r="Z41" s="49"/>
+      <c r="AA41" s="41"/>
       <c r="AB41" s="157" t="s">
         <v>65</v>
       </c>
@@ -3864,149 +3864,149 @@
       <c r="AF41" s="146"/>
       <c r="AG41" s="146"/>
       <c r="AH41" s="146"/>
-      <c r="AI41" s="40"/>
-      <c r="AJ41" s="40"/>
-      <c r="AK41" s="40"/>
-      <c r="AL41" s="40"/>
-      <c r="AM41" s="40"/>
-      <c r="AN41" s="40"/>
-      <c r="AO41" s="40"/>
-      <c r="AP41" s="40"/>
-      <c r="AQ41" s="40"/>
-      <c r="AR41" s="41"/>
+      <c r="AI41" s="36"/>
+      <c r="AJ41" s="36"/>
+      <c r="AK41" s="36"/>
+      <c r="AL41" s="36"/>
+      <c r="AM41" s="36"/>
+      <c r="AN41" s="36"/>
+      <c r="AO41" s="36"/>
+      <c r="AP41" s="36"/>
+      <c r="AQ41" s="36"/>
+      <c r="AR41" s="37"/>
     </row>
     <row r="42" spans="1:44" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="97"/>
-      <c r="B42" s="98"/>
-      <c r="C42" s="98"/>
-      <c r="D42" s="98"/>
-      <c r="E42" s="98"/>
-      <c r="F42" s="98"/>
-      <c r="G42" s="98"/>
-      <c r="H42" s="98"/>
-      <c r="I42" s="98"/>
-      <c r="J42" s="98"/>
-      <c r="K42" s="98"/>
-      <c r="L42" s="98"/>
-      <c r="M42" s="98"/>
-      <c r="N42" s="98"/>
-      <c r="O42" s="98"/>
-      <c r="P42" s="98"/>
-      <c r="Q42" s="98"/>
-      <c r="R42" s="98"/>
-      <c r="S42" s="98"/>
-      <c r="T42" s="98"/>
-      <c r="U42" s="98"/>
-      <c r="V42" s="98"/>
-      <c r="W42" s="98"/>
-      <c r="X42" s="98"/>
-      <c r="Y42" s="98"/>
-      <c r="Z42" s="99"/>
-      <c r="AA42" s="101"/>
+      <c r="A42" s="47"/>
+      <c r="B42" s="48"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="48"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="48"/>
+      <c r="J42" s="48"/>
+      <c r="K42" s="48"/>
+      <c r="L42" s="48"/>
+      <c r="M42" s="48"/>
+      <c r="N42" s="48"/>
+      <c r="O42" s="48"/>
+      <c r="P42" s="48"/>
+      <c r="Q42" s="48"/>
+      <c r="R42" s="48"/>
+      <c r="S42" s="48"/>
+      <c r="T42" s="48"/>
+      <c r="U42" s="48"/>
+      <c r="V42" s="48"/>
+      <c r="W42" s="48"/>
+      <c r="X42" s="48"/>
+      <c r="Y42" s="48"/>
+      <c r="Z42" s="49"/>
+      <c r="AA42" s="41"/>
       <c r="AB42" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="AC42" s="40"/>
-      <c r="AD42" s="40"/>
-      <c r="AE42" s="40"/>
-      <c r="AF42" s="40"/>
-      <c r="AG42" s="40"/>
-      <c r="AH42" s="40"/>
-      <c r="AI42" s="40"/>
-      <c r="AJ42" s="40"/>
-      <c r="AK42" s="40"/>
-      <c r="AL42" s="40"/>
-      <c r="AM42" s="40"/>
-      <c r="AN42" s="40"/>
+      <c r="AC42" s="36"/>
+      <c r="AD42" s="36"/>
+      <c r="AE42" s="36"/>
+      <c r="AF42" s="36"/>
+      <c r="AG42" s="36"/>
+      <c r="AH42" s="36"/>
+      <c r="AI42" s="36"/>
+      <c r="AJ42" s="36"/>
+      <c r="AK42" s="36"/>
+      <c r="AL42" s="36"/>
+      <c r="AM42" s="36"/>
+      <c r="AN42" s="36"/>
       <c r="AO42" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="AP42" s="40"/>
-      <c r="AQ42" s="40"/>
-      <c r="AR42" s="41"/>
+      <c r="AP42" s="36"/>
+      <c r="AQ42" s="36"/>
+      <c r="AR42" s="37"/>
     </row>
     <row r="43" spans="1:44" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="44" t="s">
+      <c r="A43" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="32"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="48" t="s">
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="L43" s="32"/>
-      <c r="M43" s="32"/>
-      <c r="N43" s="32"/>
-      <c r="O43" s="32"/>
-      <c r="P43" s="32"/>
-      <c r="Q43" s="32"/>
-      <c r="R43" s="32"/>
-      <c r="S43" s="32"/>
-      <c r="T43" s="32"/>
-      <c r="U43" s="32"/>
-      <c r="V43" s="32"/>
-      <c r="W43" s="32"/>
-      <c r="X43" s="32"/>
-      <c r="Y43" s="32"/>
-      <c r="Z43" s="43"/>
-      <c r="AA43" s="101"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="28"/>
+      <c r="T43" s="28"/>
+      <c r="U43" s="28"/>
+      <c r="V43" s="28"/>
+      <c r="W43" s="28"/>
+      <c r="X43" s="28"/>
+      <c r="Y43" s="28"/>
+      <c r="Z43" s="39"/>
+      <c r="AA43" s="41"/>
       <c r="AB43" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="AC43" s="40"/>
-      <c r="AD43" s="40"/>
-      <c r="AE43" s="40"/>
-      <c r="AF43" s="40"/>
-      <c r="AG43" s="40"/>
-      <c r="AH43" s="40"/>
-      <c r="AI43" s="40"/>
-      <c r="AJ43" s="40"/>
-      <c r="AK43" s="40"/>
-      <c r="AL43" s="40"/>
-      <c r="AM43" s="40"/>
-      <c r="AN43" s="40"/>
-      <c r="AO43" s="40"/>
-      <c r="AP43" s="40"/>
-      <c r="AQ43" s="40"/>
-      <c r="AR43" s="41"/>
+      <c r="AC43" s="36"/>
+      <c r="AD43" s="36"/>
+      <c r="AE43" s="36"/>
+      <c r="AF43" s="36"/>
+      <c r="AG43" s="36"/>
+      <c r="AH43" s="36"/>
+      <c r="AI43" s="36"/>
+      <c r="AJ43" s="36"/>
+      <c r="AK43" s="36"/>
+      <c r="AL43" s="36"/>
+      <c r="AM43" s="36"/>
+      <c r="AN43" s="36"/>
+      <c r="AO43" s="36"/>
+      <c r="AP43" s="36"/>
+      <c r="AQ43" s="36"/>
+      <c r="AR43" s="37"/>
     </row>
     <row r="44" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="93" t="s">
+      <c r="A44" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="B44" s="94"/>
-      <c r="C44" s="94"/>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
-      <c r="F44" s="94"/>
-      <c r="G44" s="94"/>
-      <c r="H44" s="94"/>
-      <c r="I44" s="94"/>
-      <c r="J44" s="94"/>
-      <c r="K44" s="95"/>
-      <c r="L44" s="94"/>
-      <c r="M44" s="94"/>
-      <c r="N44" s="94"/>
-      <c r="O44" s="94"/>
-      <c r="P44" s="94"/>
-      <c r="Q44" s="94"/>
-      <c r="R44" s="94"/>
-      <c r="S44" s="94"/>
-      <c r="T44" s="94"/>
-      <c r="U44" s="94"/>
-      <c r="V44" s="94"/>
-      <c r="W44" s="94"/>
-      <c r="X44" s="94"/>
-      <c r="Y44" s="94"/>
-      <c r="Z44" s="96"/>
-      <c r="AA44" s="102"/>
+      <c r="B44" s="102"/>
+      <c r="C44" s="102"/>
+      <c r="D44" s="102"/>
+      <c r="E44" s="102"/>
+      <c r="F44" s="102"/>
+      <c r="G44" s="102"/>
+      <c r="H44" s="102"/>
+      <c r="I44" s="102"/>
+      <c r="J44" s="102"/>
+      <c r="K44" s="103"/>
+      <c r="L44" s="102"/>
+      <c r="M44" s="102"/>
+      <c r="N44" s="102"/>
+      <c r="O44" s="102"/>
+      <c r="P44" s="102"/>
+      <c r="Q44" s="102"/>
+      <c r="R44" s="102"/>
+      <c r="S44" s="102"/>
+      <c r="T44" s="102"/>
+      <c r="U44" s="102"/>
+      <c r="V44" s="102"/>
+      <c r="W44" s="102"/>
+      <c r="X44" s="102"/>
+      <c r="Y44" s="102"/>
+      <c r="Z44" s="104"/>
+      <c r="AA44" s="42"/>
       <c r="AB44" s="23"/>
       <c r="AC44" s="158"/>
       <c r="AD44" s="158"/>
@@ -4025,68 +4025,653 @@
       <c r="AQ44" s="158"/>
       <c r="AR44" s="159"/>
     </row>
-    <row r="45" spans="1:44" ht="28.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:44" ht="28.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:44" ht="28.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:44" ht="28" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="1:44" ht="28" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:44" ht="28" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="1:44" ht="28" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="1:44" ht="28" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:44" ht="28" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:44" ht="28" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:44" ht="28" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:44" ht="28" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:44" ht="28.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="58" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="153" t="s">
+    <row r="45" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="153" t="s">
         <v>88</v>
       </c>
-      <c r="B58" s="154"/>
-      <c r="C58" s="154"/>
-      <c r="D58" s="154"/>
-      <c r="E58" s="154"/>
-      <c r="F58" s="154"/>
-      <c r="G58" s="154"/>
-      <c r="H58" s="154"/>
-      <c r="I58" s="154"/>
-      <c r="J58" s="154"/>
-      <c r="K58" s="154"/>
-      <c r="L58" s="154"/>
-      <c r="M58" s="154"/>
-      <c r="N58" s="154"/>
-      <c r="O58" s="154"/>
-      <c r="P58" s="154"/>
-      <c r="Q58" s="154"/>
-      <c r="R58" s="154"/>
-      <c r="S58" s="154"/>
-      <c r="T58" s="154"/>
-      <c r="U58" s="154"/>
-      <c r="V58" s="154"/>
-      <c r="W58" s="154"/>
-      <c r="X58" s="154"/>
-      <c r="Y58" s="154"/>
-      <c r="Z58" s="154"/>
-      <c r="AA58" s="154"/>
-      <c r="AB58" s="154"/>
-      <c r="AC58" s="154"/>
-      <c r="AD58" s="154"/>
-      <c r="AE58" s="154"/>
-      <c r="AF58" s="154"/>
-      <c r="AG58" s="154"/>
-      <c r="AH58" s="154"/>
-      <c r="AI58" s="154"/>
-      <c r="AJ58" s="154"/>
-      <c r="AK58" s="154"/>
-      <c r="AL58" s="154"/>
-      <c r="AM58" s="154"/>
-      <c r="AN58" s="154"/>
-      <c r="AO58" s="154"/>
-      <c r="AP58" s="154"/>
-      <c r="AQ58" s="154"/>
-      <c r="AR58" s="155"/>
-    </row>
-    <row r="59" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="154"/>
+      <c r="C45" s="154"/>
+      <c r="D45" s="154"/>
+      <c r="E45" s="154"/>
+      <c r="F45" s="154"/>
+      <c r="G45" s="154"/>
+      <c r="H45" s="154"/>
+      <c r="I45" s="154"/>
+      <c r="J45" s="154"/>
+      <c r="K45" s="154"/>
+      <c r="L45" s="154"/>
+      <c r="M45" s="154"/>
+      <c r="N45" s="154"/>
+      <c r="O45" s="154"/>
+      <c r="P45" s="154"/>
+      <c r="Q45" s="154"/>
+      <c r="R45" s="154"/>
+      <c r="S45" s="154"/>
+      <c r="T45" s="154"/>
+      <c r="U45" s="154"/>
+      <c r="V45" s="154"/>
+      <c r="W45" s="154"/>
+      <c r="X45" s="154"/>
+      <c r="Y45" s="154"/>
+      <c r="Z45" s="154"/>
+      <c r="AA45" s="154"/>
+      <c r="AB45" s="154"/>
+      <c r="AC45" s="154"/>
+      <c r="AD45" s="154"/>
+      <c r="AE45" s="154"/>
+      <c r="AF45" s="154"/>
+      <c r="AG45" s="154"/>
+      <c r="AH45" s="154"/>
+      <c r="AI45" s="154"/>
+      <c r="AJ45" s="154"/>
+      <c r="AK45" s="154"/>
+      <c r="AL45" s="154"/>
+      <c r="AM45" s="154"/>
+      <c r="AN45" s="154"/>
+      <c r="AO45" s="154"/>
+      <c r="AP45" s="154"/>
+      <c r="AQ45" s="154"/>
+      <c r="AR45" s="155"/>
+    </row>
+    <row r="46" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="147"/>
+      <c r="B46" s="148"/>
+      <c r="C46" s="148"/>
+      <c r="D46" s="148"/>
+      <c r="E46" s="148"/>
+      <c r="F46" s="148"/>
+      <c r="G46" s="148"/>
+      <c r="H46" s="148"/>
+      <c r="I46" s="148"/>
+      <c r="J46" s="148"/>
+      <c r="K46" s="148"/>
+      <c r="L46" s="148"/>
+      <c r="M46" s="148"/>
+      <c r="N46" s="148"/>
+      <c r="O46" s="148"/>
+      <c r="P46" s="148"/>
+      <c r="Q46" s="148"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="148"/>
+      <c r="T46" s="148"/>
+      <c r="U46" s="148"/>
+      <c r="V46" s="148"/>
+      <c r="W46" s="148"/>
+      <c r="X46" s="148"/>
+      <c r="Y46" s="148"/>
+      <c r="Z46" s="148"/>
+      <c r="AA46" s="148"/>
+      <c r="AB46" s="148"/>
+      <c r="AC46" s="148"/>
+      <c r="AD46" s="148"/>
+      <c r="AE46" s="148"/>
+      <c r="AF46" s="148"/>
+      <c r="AG46" s="148"/>
+      <c r="AH46" s="148"/>
+      <c r="AI46" s="148"/>
+      <c r="AJ46" s="148"/>
+      <c r="AK46" s="148"/>
+      <c r="AL46" s="148"/>
+      <c r="AM46" s="148"/>
+      <c r="AN46" s="148"/>
+      <c r="AO46" s="148"/>
+      <c r="AP46" s="148"/>
+      <c r="AQ46" s="148"/>
+      <c r="AR46" s="149"/>
+    </row>
+    <row r="47" spans="1:44" ht="8.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="150"/>
+      <c r="B47" s="151"/>
+      <c r="C47" s="151"/>
+      <c r="D47" s="151"/>
+      <c r="E47" s="151"/>
+      <c r="F47" s="151"/>
+      <c r="G47" s="151"/>
+      <c r="H47" s="151"/>
+      <c r="I47" s="151"/>
+      <c r="J47" s="151"/>
+      <c r="K47" s="151"/>
+      <c r="L47" s="151"/>
+      <c r="M47" s="151"/>
+      <c r="N47" s="151"/>
+      <c r="O47" s="151"/>
+      <c r="P47" s="151"/>
+      <c r="Q47" s="151"/>
+      <c r="R47" s="151"/>
+      <c r="S47" s="151"/>
+      <c r="T47" s="151"/>
+      <c r="U47" s="151"/>
+      <c r="V47" s="151"/>
+      <c r="W47" s="151"/>
+      <c r="X47" s="151"/>
+      <c r="Y47" s="151"/>
+      <c r="Z47" s="151"/>
+      <c r="AA47" s="151"/>
+      <c r="AB47" s="151"/>
+      <c r="AC47" s="151"/>
+      <c r="AD47" s="151"/>
+      <c r="AE47" s="151"/>
+      <c r="AF47" s="151"/>
+      <c r="AG47" s="151"/>
+      <c r="AH47" s="151"/>
+      <c r="AI47" s="151"/>
+      <c r="AJ47" s="151"/>
+      <c r="AK47" s="151"/>
+      <c r="AL47" s="151"/>
+      <c r="AM47" s="151"/>
+      <c r="AN47" s="151"/>
+      <c r="AO47" s="151"/>
+      <c r="AP47" s="151"/>
+      <c r="AQ47" s="151"/>
+      <c r="AR47" s="152"/>
+    </row>
+    <row r="48" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="147"/>
+      <c r="B48" s="148"/>
+      <c r="C48" s="148"/>
+      <c r="D48" s="148"/>
+      <c r="E48" s="148"/>
+      <c r="F48" s="148"/>
+      <c r="G48" s="148"/>
+      <c r="H48" s="148"/>
+      <c r="I48" s="148"/>
+      <c r="J48" s="148"/>
+      <c r="K48" s="148"/>
+      <c r="L48" s="148"/>
+      <c r="M48" s="148"/>
+      <c r="N48" s="148"/>
+      <c r="O48" s="148"/>
+      <c r="P48" s="148"/>
+      <c r="Q48" s="148"/>
+      <c r="R48" s="148"/>
+      <c r="S48" s="148"/>
+      <c r="T48" s="148"/>
+      <c r="U48" s="148"/>
+      <c r="V48" s="148"/>
+      <c r="W48" s="148"/>
+      <c r="X48" s="148"/>
+      <c r="Y48" s="148"/>
+      <c r="Z48" s="148"/>
+      <c r="AA48" s="148"/>
+      <c r="AB48" s="148"/>
+      <c r="AC48" s="148"/>
+      <c r="AD48" s="148"/>
+      <c r="AE48" s="148"/>
+      <c r="AF48" s="148"/>
+      <c r="AG48" s="148"/>
+      <c r="AH48" s="148"/>
+      <c r="AI48" s="148"/>
+      <c r="AJ48" s="148"/>
+      <c r="AK48" s="148"/>
+      <c r="AL48" s="148"/>
+      <c r="AM48" s="148"/>
+      <c r="AN48" s="148"/>
+      <c r="AO48" s="148"/>
+      <c r="AP48" s="148"/>
+      <c r="AQ48" s="148"/>
+      <c r="AR48" s="149"/>
+    </row>
+    <row r="49" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="147"/>
+      <c r="B49" s="148"/>
+      <c r="C49" s="148"/>
+      <c r="D49" s="148"/>
+      <c r="E49" s="148"/>
+      <c r="F49" s="148"/>
+      <c r="G49" s="148"/>
+      <c r="H49" s="148"/>
+      <c r="I49" s="148"/>
+      <c r="J49" s="148"/>
+      <c r="K49" s="148"/>
+      <c r="L49" s="148"/>
+      <c r="M49" s="148"/>
+      <c r="N49" s="148"/>
+      <c r="O49" s="148"/>
+      <c r="P49" s="148"/>
+      <c r="Q49" s="148"/>
+      <c r="R49" s="148"/>
+      <c r="S49" s="148"/>
+      <c r="T49" s="148"/>
+      <c r="U49" s="148"/>
+      <c r="V49" s="148"/>
+      <c r="W49" s="148"/>
+      <c r="X49" s="148"/>
+      <c r="Y49" s="148"/>
+      <c r="Z49" s="148"/>
+      <c r="AA49" s="148"/>
+      <c r="AB49" s="148"/>
+      <c r="AC49" s="148"/>
+      <c r="AD49" s="148"/>
+      <c r="AE49" s="148"/>
+      <c r="AF49" s="148"/>
+      <c r="AG49" s="148"/>
+      <c r="AH49" s="148"/>
+      <c r="AI49" s="148"/>
+      <c r="AJ49" s="148"/>
+      <c r="AK49" s="148"/>
+      <c r="AL49" s="148"/>
+      <c r="AM49" s="148"/>
+      <c r="AN49" s="148"/>
+      <c r="AO49" s="148"/>
+      <c r="AP49" s="148"/>
+      <c r="AQ49" s="148"/>
+      <c r="AR49" s="149"/>
+    </row>
+    <row r="50" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="147"/>
+      <c r="B50" s="148"/>
+      <c r="C50" s="148"/>
+      <c r="D50" s="148"/>
+      <c r="E50" s="148"/>
+      <c r="F50" s="148"/>
+      <c r="G50" s="148"/>
+      <c r="H50" s="148"/>
+      <c r="I50" s="148"/>
+      <c r="J50" s="148"/>
+      <c r="K50" s="148"/>
+      <c r="L50" s="148"/>
+      <c r="M50" s="148"/>
+      <c r="N50" s="148"/>
+      <c r="O50" s="148"/>
+      <c r="P50" s="148"/>
+      <c r="Q50" s="148"/>
+      <c r="R50" s="148"/>
+      <c r="S50" s="148"/>
+      <c r="T50" s="148"/>
+      <c r="U50" s="148"/>
+      <c r="V50" s="148"/>
+      <c r="W50" s="148"/>
+      <c r="X50" s="148"/>
+      <c r="Y50" s="148"/>
+      <c r="Z50" s="148"/>
+      <c r="AA50" s="148"/>
+      <c r="AB50" s="148"/>
+      <c r="AC50" s="148"/>
+      <c r="AD50" s="148"/>
+      <c r="AE50" s="148"/>
+      <c r="AF50" s="148"/>
+      <c r="AG50" s="148"/>
+      <c r="AH50" s="148"/>
+      <c r="AI50" s="148"/>
+      <c r="AJ50" s="148"/>
+      <c r="AK50" s="148"/>
+      <c r="AL50" s="148"/>
+      <c r="AM50" s="148"/>
+      <c r="AN50" s="148"/>
+      <c r="AO50" s="148"/>
+      <c r="AP50" s="148"/>
+      <c r="AQ50" s="148"/>
+      <c r="AR50" s="149"/>
+    </row>
+    <row r="51" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="147"/>
+      <c r="B51" s="148"/>
+      <c r="C51" s="148"/>
+      <c r="D51" s="148"/>
+      <c r="E51" s="148"/>
+      <c r="F51" s="148"/>
+      <c r="G51" s="148"/>
+      <c r="H51" s="148"/>
+      <c r="I51" s="148"/>
+      <c r="J51" s="148"/>
+      <c r="K51" s="148"/>
+      <c r="L51" s="148"/>
+      <c r="M51" s="148"/>
+      <c r="N51" s="148"/>
+      <c r="O51" s="148"/>
+      <c r="P51" s="148"/>
+      <c r="Q51" s="148"/>
+      <c r="R51" s="148"/>
+      <c r="S51" s="148"/>
+      <c r="T51" s="148"/>
+      <c r="U51" s="148"/>
+      <c r="V51" s="148"/>
+      <c r="W51" s="148"/>
+      <c r="X51" s="148"/>
+      <c r="Y51" s="148"/>
+      <c r="Z51" s="148"/>
+      <c r="AA51" s="148"/>
+      <c r="AB51" s="148"/>
+      <c r="AC51" s="148"/>
+      <c r="AD51" s="148"/>
+      <c r="AE51" s="148"/>
+      <c r="AF51" s="148"/>
+      <c r="AG51" s="148"/>
+      <c r="AH51" s="148"/>
+      <c r="AI51" s="148"/>
+      <c r="AJ51" s="148"/>
+      <c r="AK51" s="148"/>
+      <c r="AL51" s="148"/>
+      <c r="AM51" s="148"/>
+      <c r="AN51" s="148"/>
+      <c r="AO51" s="148"/>
+      <c r="AP51" s="148"/>
+      <c r="AQ51" s="148"/>
+      <c r="AR51" s="149"/>
+    </row>
+    <row r="52" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="147"/>
+      <c r="B52" s="148"/>
+      <c r="C52" s="148"/>
+      <c r="D52" s="148"/>
+      <c r="E52" s="148"/>
+      <c r="F52" s="148"/>
+      <c r="G52" s="148"/>
+      <c r="H52" s="148"/>
+      <c r="I52" s="148"/>
+      <c r="J52" s="148"/>
+      <c r="K52" s="148"/>
+      <c r="L52" s="148"/>
+      <c r="M52" s="148"/>
+      <c r="N52" s="148"/>
+      <c r="O52" s="148"/>
+      <c r="P52" s="148"/>
+      <c r="Q52" s="148"/>
+      <c r="R52" s="148"/>
+      <c r="S52" s="148"/>
+      <c r="T52" s="148"/>
+      <c r="U52" s="148"/>
+      <c r="V52" s="148"/>
+      <c r="W52" s="148"/>
+      <c r="X52" s="148"/>
+      <c r="Y52" s="148"/>
+      <c r="Z52" s="148"/>
+      <c r="AA52" s="148"/>
+      <c r="AB52" s="148"/>
+      <c r="AC52" s="148"/>
+      <c r="AD52" s="148"/>
+      <c r="AE52" s="148"/>
+      <c r="AF52" s="148"/>
+      <c r="AG52" s="148"/>
+      <c r="AH52" s="148"/>
+      <c r="AI52" s="148"/>
+      <c r="AJ52" s="148"/>
+      <c r="AK52" s="148"/>
+      <c r="AL52" s="148"/>
+      <c r="AM52" s="148"/>
+      <c r="AN52" s="148"/>
+      <c r="AO52" s="148"/>
+      <c r="AP52" s="148"/>
+      <c r="AQ52" s="148"/>
+      <c r="AR52" s="149"/>
+    </row>
+    <row r="53" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="147"/>
+      <c r="B53" s="148"/>
+      <c r="C53" s="148"/>
+      <c r="D53" s="148"/>
+      <c r="E53" s="148"/>
+      <c r="F53" s="148"/>
+      <c r="G53" s="148"/>
+      <c r="H53" s="148"/>
+      <c r="I53" s="148"/>
+      <c r="J53" s="148"/>
+      <c r="K53" s="148"/>
+      <c r="L53" s="148"/>
+      <c r="M53" s="148"/>
+      <c r="N53" s="148"/>
+      <c r="O53" s="148"/>
+      <c r="P53" s="148"/>
+      <c r="Q53" s="148"/>
+      <c r="R53" s="148"/>
+      <c r="S53" s="148"/>
+      <c r="T53" s="148"/>
+      <c r="U53" s="148"/>
+      <c r="V53" s="148"/>
+      <c r="W53" s="148"/>
+      <c r="X53" s="148"/>
+      <c r="Y53" s="148"/>
+      <c r="Z53" s="148"/>
+      <c r="AA53" s="148"/>
+      <c r="AB53" s="148"/>
+      <c r="AC53" s="148"/>
+      <c r="AD53" s="148"/>
+      <c r="AE53" s="148"/>
+      <c r="AF53" s="148"/>
+      <c r="AG53" s="148"/>
+      <c r="AH53" s="148"/>
+      <c r="AI53" s="148"/>
+      <c r="AJ53" s="148"/>
+      <c r="AK53" s="148"/>
+      <c r="AL53" s="148"/>
+      <c r="AM53" s="148"/>
+      <c r="AN53" s="148"/>
+      <c r="AO53" s="148"/>
+      <c r="AP53" s="148"/>
+      <c r="AQ53" s="148"/>
+      <c r="AR53" s="149"/>
+    </row>
+    <row r="54" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="147"/>
+      <c r="B54" s="148"/>
+      <c r="C54" s="148"/>
+      <c r="D54" s="148"/>
+      <c r="E54" s="148"/>
+      <c r="F54" s="148"/>
+      <c r="G54" s="148"/>
+      <c r="H54" s="148"/>
+      <c r="I54" s="148"/>
+      <c r="J54" s="148"/>
+      <c r="K54" s="148"/>
+      <c r="L54" s="148"/>
+      <c r="M54" s="148"/>
+      <c r="N54" s="148"/>
+      <c r="O54" s="148"/>
+      <c r="P54" s="148"/>
+      <c r="Q54" s="148"/>
+      <c r="R54" s="148"/>
+      <c r="S54" s="148"/>
+      <c r="T54" s="148"/>
+      <c r="U54" s="148"/>
+      <c r="V54" s="148"/>
+      <c r="W54" s="148"/>
+      <c r="X54" s="148"/>
+      <c r="Y54" s="148"/>
+      <c r="Z54" s="148"/>
+      <c r="AA54" s="148"/>
+      <c r="AB54" s="148"/>
+      <c r="AC54" s="148"/>
+      <c r="AD54" s="148"/>
+      <c r="AE54" s="148"/>
+      <c r="AF54" s="148"/>
+      <c r="AG54" s="148"/>
+      <c r="AH54" s="148"/>
+      <c r="AI54" s="148"/>
+      <c r="AJ54" s="148"/>
+      <c r="AK54" s="148"/>
+      <c r="AL54" s="148"/>
+      <c r="AM54" s="148"/>
+      <c r="AN54" s="148"/>
+      <c r="AO54" s="148"/>
+      <c r="AP54" s="148"/>
+      <c r="AQ54" s="148"/>
+      <c r="AR54" s="149"/>
+    </row>
+    <row r="55" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="147"/>
+      <c r="B55" s="148"/>
+      <c r="C55" s="148"/>
+      <c r="D55" s="148"/>
+      <c r="E55" s="148"/>
+      <c r="F55" s="148"/>
+      <c r="G55" s="148"/>
+      <c r="H55" s="148"/>
+      <c r="I55" s="148"/>
+      <c r="J55" s="148"/>
+      <c r="K55" s="148"/>
+      <c r="L55" s="148"/>
+      <c r="M55" s="148"/>
+      <c r="N55" s="148"/>
+      <c r="O55" s="148"/>
+      <c r="P55" s="148"/>
+      <c r="Q55" s="148"/>
+      <c r="R55" s="148"/>
+      <c r="S55" s="148"/>
+      <c r="T55" s="148"/>
+      <c r="U55" s="148"/>
+      <c r="V55" s="148"/>
+      <c r="W55" s="148"/>
+      <c r="X55" s="148"/>
+      <c r="Y55" s="148"/>
+      <c r="Z55" s="148"/>
+      <c r="AA55" s="148"/>
+      <c r="AB55" s="148"/>
+      <c r="AC55" s="148"/>
+      <c r="AD55" s="148"/>
+      <c r="AE55" s="148"/>
+      <c r="AF55" s="148"/>
+      <c r="AG55" s="148"/>
+      <c r="AH55" s="148"/>
+      <c r="AI55" s="148"/>
+      <c r="AJ55" s="148"/>
+      <c r="AK55" s="148"/>
+      <c r="AL55" s="148"/>
+      <c r="AM55" s="148"/>
+      <c r="AN55" s="148"/>
+      <c r="AO55" s="148"/>
+      <c r="AP55" s="148"/>
+      <c r="AQ55" s="148"/>
+      <c r="AR55" s="149"/>
+    </row>
+    <row r="56" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="147"/>
+      <c r="B56" s="148"/>
+      <c r="C56" s="148"/>
+      <c r="D56" s="148"/>
+      <c r="E56" s="148"/>
+      <c r="F56" s="148"/>
+      <c r="G56" s="148"/>
+      <c r="H56" s="148"/>
+      <c r="I56" s="148"/>
+      <c r="J56" s="148"/>
+      <c r="K56" s="148"/>
+      <c r="L56" s="148"/>
+      <c r="M56" s="148"/>
+      <c r="N56" s="148"/>
+      <c r="O56" s="148"/>
+      <c r="P56" s="148"/>
+      <c r="Q56" s="148"/>
+      <c r="R56" s="148"/>
+      <c r="S56" s="148"/>
+      <c r="T56" s="148"/>
+      <c r="U56" s="148"/>
+      <c r="V56" s="148"/>
+      <c r="W56" s="148"/>
+      <c r="X56" s="148"/>
+      <c r="Y56" s="148"/>
+      <c r="Z56" s="148"/>
+      <c r="AA56" s="148"/>
+      <c r="AB56" s="148"/>
+      <c r="AC56" s="148"/>
+      <c r="AD56" s="148"/>
+      <c r="AE56" s="148"/>
+      <c r="AF56" s="148"/>
+      <c r="AG56" s="148"/>
+      <c r="AH56" s="148"/>
+      <c r="AI56" s="148"/>
+      <c r="AJ56" s="148"/>
+      <c r="AK56" s="148"/>
+      <c r="AL56" s="148"/>
+      <c r="AM56" s="148"/>
+      <c r="AN56" s="148"/>
+      <c r="AO56" s="148"/>
+      <c r="AP56" s="148"/>
+      <c r="AQ56" s="148"/>
+      <c r="AR56" s="149"/>
+    </row>
+    <row r="57" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="147"/>
+      <c r="B57" s="148"/>
+      <c r="C57" s="148"/>
+      <c r="D57" s="148"/>
+      <c r="E57" s="148"/>
+      <c r="F57" s="148"/>
+      <c r="G57" s="148"/>
+      <c r="H57" s="148"/>
+      <c r="I57" s="148"/>
+      <c r="J57" s="148"/>
+      <c r="K57" s="148"/>
+      <c r="L57" s="148"/>
+      <c r="M57" s="148"/>
+      <c r="N57" s="148"/>
+      <c r="O57" s="148"/>
+      <c r="P57" s="148"/>
+      <c r="Q57" s="148"/>
+      <c r="R57" s="148"/>
+      <c r="S57" s="148"/>
+      <c r="T57" s="148"/>
+      <c r="U57" s="148"/>
+      <c r="V57" s="148"/>
+      <c r="W57" s="148"/>
+      <c r="X57" s="148"/>
+      <c r="Y57" s="148"/>
+      <c r="Z57" s="148"/>
+      <c r="AA57" s="148"/>
+      <c r="AB57" s="148"/>
+      <c r="AC57" s="148"/>
+      <c r="AD57" s="148"/>
+      <c r="AE57" s="148"/>
+      <c r="AF57" s="148"/>
+      <c r="AG57" s="148"/>
+      <c r="AH57" s="148"/>
+      <c r="AI57" s="148"/>
+      <c r="AJ57" s="148"/>
+      <c r="AK57" s="148"/>
+      <c r="AL57" s="148"/>
+      <c r="AM57" s="148"/>
+      <c r="AN57" s="148"/>
+      <c r="AO57" s="148"/>
+      <c r="AP57" s="148"/>
+      <c r="AQ57" s="148"/>
+      <c r="AR57" s="149"/>
+    </row>
+    <row r="58" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="147"/>
+      <c r="B58" s="148"/>
+      <c r="C58" s="148"/>
+      <c r="D58" s="148"/>
+      <c r="E58" s="148"/>
+      <c r="F58" s="148"/>
+      <c r="G58" s="148"/>
+      <c r="H58" s="148"/>
+      <c r="I58" s="148"/>
+      <c r="J58" s="148"/>
+      <c r="K58" s="148"/>
+      <c r="L58" s="148"/>
+      <c r="M58" s="148"/>
+      <c r="N58" s="148"/>
+      <c r="O58" s="148"/>
+      <c r="P58" s="148"/>
+      <c r="Q58" s="148"/>
+      <c r="R58" s="148"/>
+      <c r="S58" s="148"/>
+      <c r="T58" s="148"/>
+      <c r="U58" s="148"/>
+      <c r="V58" s="148"/>
+      <c r="W58" s="148"/>
+      <c r="X58" s="148"/>
+      <c r="Y58" s="148"/>
+      <c r="Z58" s="148"/>
+      <c r="AA58" s="148"/>
+      <c r="AB58" s="148"/>
+      <c r="AC58" s="148"/>
+      <c r="AD58" s="148"/>
+      <c r="AE58" s="148"/>
+      <c r="AF58" s="148"/>
+      <c r="AG58" s="148"/>
+      <c r="AH58" s="148"/>
+      <c r="AI58" s="148"/>
+      <c r="AJ58" s="148"/>
+      <c r="AK58" s="148"/>
+      <c r="AL58" s="148"/>
+      <c r="AM58" s="148"/>
+      <c r="AN58" s="148"/>
+      <c r="AO58" s="148"/>
+      <c r="AP58" s="148"/>
+      <c r="AQ58" s="148"/>
+      <c r="AR58" s="149"/>
+    </row>
+    <row r="59" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="147"/>
       <c r="B59" s="148"/>
       <c r="C59" s="148"/>
@@ -4132,51 +4717,51 @@
       <c r="AQ59" s="148"/>
       <c r="AR59" s="149"/>
     </row>
-    <row r="60" spans="1:44" ht="8.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="150"/>
-      <c r="B60" s="151"/>
-      <c r="C60" s="151"/>
-      <c r="D60" s="151"/>
-      <c r="E60" s="151"/>
-      <c r="F60" s="151"/>
-      <c r="G60" s="151"/>
-      <c r="H60" s="151"/>
-      <c r="I60" s="151"/>
-      <c r="J60" s="151"/>
-      <c r="K60" s="151"/>
-      <c r="L60" s="151"/>
-      <c r="M60" s="151"/>
-      <c r="N60" s="151"/>
-      <c r="O60" s="151"/>
-      <c r="P60" s="151"/>
-      <c r="Q60" s="151"/>
-      <c r="R60" s="151"/>
-      <c r="S60" s="151"/>
-      <c r="T60" s="151"/>
-      <c r="U60" s="151"/>
-      <c r="V60" s="151"/>
-      <c r="W60" s="151"/>
-      <c r="X60" s="151"/>
-      <c r="Y60" s="151"/>
-      <c r="Z60" s="151"/>
-      <c r="AA60" s="151"/>
-      <c r="AB60" s="151"/>
-      <c r="AC60" s="151"/>
-      <c r="AD60" s="151"/>
-      <c r="AE60" s="151"/>
-      <c r="AF60" s="151"/>
-      <c r="AG60" s="151"/>
-      <c r="AH60" s="151"/>
-      <c r="AI60" s="151"/>
-      <c r="AJ60" s="151"/>
-      <c r="AK60" s="151"/>
-      <c r="AL60" s="151"/>
-      <c r="AM60" s="151"/>
-      <c r="AN60" s="151"/>
-      <c r="AO60" s="151"/>
-      <c r="AP60" s="151"/>
-      <c r="AQ60" s="151"/>
-      <c r="AR60" s="152"/>
+    <row r="60" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="147"/>
+      <c r="B60" s="148"/>
+      <c r="C60" s="148"/>
+      <c r="D60" s="148"/>
+      <c r="E60" s="148"/>
+      <c r="F60" s="148"/>
+      <c r="G60" s="148"/>
+      <c r="H60" s="148"/>
+      <c r="I60" s="148"/>
+      <c r="J60" s="148"/>
+      <c r="K60" s="148"/>
+      <c r="L60" s="148"/>
+      <c r="M60" s="148"/>
+      <c r="N60" s="148"/>
+      <c r="O60" s="148"/>
+      <c r="P60" s="148"/>
+      <c r="Q60" s="148"/>
+      <c r="R60" s="148"/>
+      <c r="S60" s="148"/>
+      <c r="T60" s="148"/>
+      <c r="U60" s="148"/>
+      <c r="V60" s="148"/>
+      <c r="W60" s="148"/>
+      <c r="X60" s="148"/>
+      <c r="Y60" s="148"/>
+      <c r="Z60" s="148"/>
+      <c r="AA60" s="148"/>
+      <c r="AB60" s="148"/>
+      <c r="AC60" s="148"/>
+      <c r="AD60" s="148"/>
+      <c r="AE60" s="148"/>
+      <c r="AF60" s="148"/>
+      <c r="AG60" s="148"/>
+      <c r="AH60" s="148"/>
+      <c r="AI60" s="148"/>
+      <c r="AJ60" s="148"/>
+      <c r="AK60" s="148"/>
+      <c r="AL60" s="148"/>
+      <c r="AM60" s="148"/>
+      <c r="AN60" s="148"/>
+      <c r="AO60" s="148"/>
+      <c r="AP60" s="148"/>
+      <c r="AQ60" s="148"/>
+      <c r="AR60" s="149"/>
     </row>
     <row r="61" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="147"/>
@@ -7076,649 +7661,51 @@
       <c r="AQ123" s="148"/>
       <c r="AR123" s="149"/>
     </row>
-    <row r="124" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="147"/>
-      <c r="B124" s="148"/>
-      <c r="C124" s="148"/>
-      <c r="D124" s="148"/>
-      <c r="E124" s="148"/>
-      <c r="F124" s="148"/>
-      <c r="G124" s="148"/>
-      <c r="H124" s="148"/>
-      <c r="I124" s="148"/>
-      <c r="J124" s="148"/>
-      <c r="K124" s="148"/>
-      <c r="L124" s="148"/>
-      <c r="M124" s="148"/>
-      <c r="N124" s="148"/>
-      <c r="O124" s="148"/>
-      <c r="P124" s="148"/>
-      <c r="Q124" s="148"/>
-      <c r="R124" s="148"/>
-      <c r="S124" s="148"/>
-      <c r="T124" s="148"/>
-      <c r="U124" s="148"/>
-      <c r="V124" s="148"/>
-      <c r="W124" s="148"/>
-      <c r="X124" s="148"/>
-      <c r="Y124" s="148"/>
-      <c r="Z124" s="148"/>
-      <c r="AA124" s="148"/>
-      <c r="AB124" s="148"/>
-      <c r="AC124" s="148"/>
-      <c r="AD124" s="148"/>
-      <c r="AE124" s="148"/>
-      <c r="AF124" s="148"/>
-      <c r="AG124" s="148"/>
-      <c r="AH124" s="148"/>
-      <c r="AI124" s="148"/>
-      <c r="AJ124" s="148"/>
-      <c r="AK124" s="148"/>
-      <c r="AL124" s="148"/>
-      <c r="AM124" s="148"/>
-      <c r="AN124" s="148"/>
-      <c r="AO124" s="148"/>
-      <c r="AP124" s="148"/>
-      <c r="AQ124" s="148"/>
-      <c r="AR124" s="149"/>
-    </row>
-    <row r="125" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="147"/>
-      <c r="B125" s="148"/>
-      <c r="C125" s="148"/>
-      <c r="D125" s="148"/>
-      <c r="E125" s="148"/>
-      <c r="F125" s="148"/>
-      <c r="G125" s="148"/>
-      <c r="H125" s="148"/>
-      <c r="I125" s="148"/>
-      <c r="J125" s="148"/>
-      <c r="K125" s="148"/>
-      <c r="L125" s="148"/>
-      <c r="M125" s="148"/>
-      <c r="N125" s="148"/>
-      <c r="O125" s="148"/>
-      <c r="P125" s="148"/>
-      <c r="Q125" s="148"/>
-      <c r="R125" s="148"/>
-      <c r="S125" s="148"/>
-      <c r="T125" s="148"/>
-      <c r="U125" s="148"/>
-      <c r="V125" s="148"/>
-      <c r="W125" s="148"/>
-      <c r="X125" s="148"/>
-      <c r="Y125" s="148"/>
-      <c r="Z125" s="148"/>
-      <c r="AA125" s="148"/>
-      <c r="AB125" s="148"/>
-      <c r="AC125" s="148"/>
-      <c r="AD125" s="148"/>
-      <c r="AE125" s="148"/>
-      <c r="AF125" s="148"/>
-      <c r="AG125" s="148"/>
-      <c r="AH125" s="148"/>
-      <c r="AI125" s="148"/>
-      <c r="AJ125" s="148"/>
-      <c r="AK125" s="148"/>
-      <c r="AL125" s="148"/>
-      <c r="AM125" s="148"/>
-      <c r="AN125" s="148"/>
-      <c r="AO125" s="148"/>
-      <c r="AP125" s="148"/>
-      <c r="AQ125" s="148"/>
-      <c r="AR125" s="149"/>
-    </row>
-    <row r="126" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="147"/>
-      <c r="B126" s="148"/>
-      <c r="C126" s="148"/>
-      <c r="D126" s="148"/>
-      <c r="E126" s="148"/>
-      <c r="F126" s="148"/>
-      <c r="G126" s="148"/>
-      <c r="H126" s="148"/>
-      <c r="I126" s="148"/>
-      <c r="J126" s="148"/>
-      <c r="K126" s="148"/>
-      <c r="L126" s="148"/>
-      <c r="M126" s="148"/>
-      <c r="N126" s="148"/>
-      <c r="O126" s="148"/>
-      <c r="P126" s="148"/>
-      <c r="Q126" s="148"/>
-      <c r="R126" s="148"/>
-      <c r="S126" s="148"/>
-      <c r="T126" s="148"/>
-      <c r="U126" s="148"/>
-      <c r="V126" s="148"/>
-      <c r="W126" s="148"/>
-      <c r="X126" s="148"/>
-      <c r="Y126" s="148"/>
-      <c r="Z126" s="148"/>
-      <c r="AA126" s="148"/>
-      <c r="AB126" s="148"/>
-      <c r="AC126" s="148"/>
-      <c r="AD126" s="148"/>
-      <c r="AE126" s="148"/>
-      <c r="AF126" s="148"/>
-      <c r="AG126" s="148"/>
-      <c r="AH126" s="148"/>
-      <c r="AI126" s="148"/>
-      <c r="AJ126" s="148"/>
-      <c r="AK126" s="148"/>
-      <c r="AL126" s="148"/>
-      <c r="AM126" s="148"/>
-      <c r="AN126" s="148"/>
-      <c r="AO126" s="148"/>
-      <c r="AP126" s="148"/>
-      <c r="AQ126" s="148"/>
-      <c r="AR126" s="149"/>
-    </row>
-    <row r="127" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="147"/>
-      <c r="B127" s="148"/>
-      <c r="C127" s="148"/>
-      <c r="D127" s="148"/>
-      <c r="E127" s="148"/>
-      <c r="F127" s="148"/>
-      <c r="G127" s="148"/>
-      <c r="H127" s="148"/>
-      <c r="I127" s="148"/>
-      <c r="J127" s="148"/>
-      <c r="K127" s="148"/>
-      <c r="L127" s="148"/>
-      <c r="M127" s="148"/>
-      <c r="N127" s="148"/>
-      <c r="O127" s="148"/>
-      <c r="P127" s="148"/>
-      <c r="Q127" s="148"/>
-      <c r="R127" s="148"/>
-      <c r="S127" s="148"/>
-      <c r="T127" s="148"/>
-      <c r="U127" s="148"/>
-      <c r="V127" s="148"/>
-      <c r="W127" s="148"/>
-      <c r="X127" s="148"/>
-      <c r="Y127" s="148"/>
-      <c r="Z127" s="148"/>
-      <c r="AA127" s="148"/>
-      <c r="AB127" s="148"/>
-      <c r="AC127" s="148"/>
-      <c r="AD127" s="148"/>
-      <c r="AE127" s="148"/>
-      <c r="AF127" s="148"/>
-      <c r="AG127" s="148"/>
-      <c r="AH127" s="148"/>
-      <c r="AI127" s="148"/>
-      <c r="AJ127" s="148"/>
-      <c r="AK127" s="148"/>
-      <c r="AL127" s="148"/>
-      <c r="AM127" s="148"/>
-      <c r="AN127" s="148"/>
-      <c r="AO127" s="148"/>
-      <c r="AP127" s="148"/>
-      <c r="AQ127" s="148"/>
-      <c r="AR127" s="149"/>
-    </row>
-    <row r="128" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="147"/>
-      <c r="B128" s="148"/>
-      <c r="C128" s="148"/>
-      <c r="D128" s="148"/>
-      <c r="E128" s="148"/>
-      <c r="F128" s="148"/>
-      <c r="G128" s="148"/>
-      <c r="H128" s="148"/>
-      <c r="I128" s="148"/>
-      <c r="J128" s="148"/>
-      <c r="K128" s="148"/>
-      <c r="L128" s="148"/>
-      <c r="M128" s="148"/>
-      <c r="N128" s="148"/>
-      <c r="O128" s="148"/>
-      <c r="P128" s="148"/>
-      <c r="Q128" s="148"/>
-      <c r="R128" s="148"/>
-      <c r="S128" s="148"/>
-      <c r="T128" s="148"/>
-      <c r="U128" s="148"/>
-      <c r="V128" s="148"/>
-      <c r="W128" s="148"/>
-      <c r="X128" s="148"/>
-      <c r="Y128" s="148"/>
-      <c r="Z128" s="148"/>
-      <c r="AA128" s="148"/>
-      <c r="AB128" s="148"/>
-      <c r="AC128" s="148"/>
-      <c r="AD128" s="148"/>
-      <c r="AE128" s="148"/>
-      <c r="AF128" s="148"/>
-      <c r="AG128" s="148"/>
-      <c r="AH128" s="148"/>
-      <c r="AI128" s="148"/>
-      <c r="AJ128" s="148"/>
-      <c r="AK128" s="148"/>
-      <c r="AL128" s="148"/>
-      <c r="AM128" s="148"/>
-      <c r="AN128" s="148"/>
-      <c r="AO128" s="148"/>
-      <c r="AP128" s="148"/>
-      <c r="AQ128" s="148"/>
-      <c r="AR128" s="149"/>
-    </row>
-    <row r="129" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="147"/>
-      <c r="B129" s="148"/>
-      <c r="C129" s="148"/>
-      <c r="D129" s="148"/>
-      <c r="E129" s="148"/>
-      <c r="F129" s="148"/>
-      <c r="G129" s="148"/>
-      <c r="H129" s="148"/>
-      <c r="I129" s="148"/>
-      <c r="J129" s="148"/>
-      <c r="K129" s="148"/>
-      <c r="L129" s="148"/>
-      <c r="M129" s="148"/>
-      <c r="N129" s="148"/>
-      <c r="O129" s="148"/>
-      <c r="P129" s="148"/>
-      <c r="Q129" s="148"/>
-      <c r="R129" s="148"/>
-      <c r="S129" s="148"/>
-      <c r="T129" s="148"/>
-      <c r="U129" s="148"/>
-      <c r="V129" s="148"/>
-      <c r="W129" s="148"/>
-      <c r="X129" s="148"/>
-      <c r="Y129" s="148"/>
-      <c r="Z129" s="148"/>
-      <c r="AA129" s="148"/>
-      <c r="AB129" s="148"/>
-      <c r="AC129" s="148"/>
-      <c r="AD129" s="148"/>
-      <c r="AE129" s="148"/>
-      <c r="AF129" s="148"/>
-      <c r="AG129" s="148"/>
-      <c r="AH129" s="148"/>
-      <c r="AI129" s="148"/>
-      <c r="AJ129" s="148"/>
-      <c r="AK129" s="148"/>
-      <c r="AL129" s="148"/>
-      <c r="AM129" s="148"/>
-      <c r="AN129" s="148"/>
-      <c r="AO129" s="148"/>
-      <c r="AP129" s="148"/>
-      <c r="AQ129" s="148"/>
-      <c r="AR129" s="149"/>
-    </row>
-    <row r="130" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="147"/>
-      <c r="B130" s="148"/>
-      <c r="C130" s="148"/>
-      <c r="D130" s="148"/>
-      <c r="E130" s="148"/>
-      <c r="F130" s="148"/>
-      <c r="G130" s="148"/>
-      <c r="H130" s="148"/>
-      <c r="I130" s="148"/>
-      <c r="J130" s="148"/>
-      <c r="K130" s="148"/>
-      <c r="L130" s="148"/>
-      <c r="M130" s="148"/>
-      <c r="N130" s="148"/>
-      <c r="O130" s="148"/>
-      <c r="P130" s="148"/>
-      <c r="Q130" s="148"/>
-      <c r="R130" s="148"/>
-      <c r="S130" s="148"/>
-      <c r="T130" s="148"/>
-      <c r="U130" s="148"/>
-      <c r="V130" s="148"/>
-      <c r="W130" s="148"/>
-      <c r="X130" s="148"/>
-      <c r="Y130" s="148"/>
-      <c r="Z130" s="148"/>
-      <c r="AA130" s="148"/>
-      <c r="AB130" s="148"/>
-      <c r="AC130" s="148"/>
-      <c r="AD130" s="148"/>
-      <c r="AE130" s="148"/>
-      <c r="AF130" s="148"/>
-      <c r="AG130" s="148"/>
-      <c r="AH130" s="148"/>
-      <c r="AI130" s="148"/>
-      <c r="AJ130" s="148"/>
-      <c r="AK130" s="148"/>
-      <c r="AL130" s="148"/>
-      <c r="AM130" s="148"/>
-      <c r="AN130" s="148"/>
-      <c r="AO130" s="148"/>
-      <c r="AP130" s="148"/>
-      <c r="AQ130" s="148"/>
-      <c r="AR130" s="149"/>
-    </row>
-    <row r="131" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="147"/>
-      <c r="B131" s="148"/>
-      <c r="C131" s="148"/>
-      <c r="D131" s="148"/>
-      <c r="E131" s="148"/>
-      <c r="F131" s="148"/>
-      <c r="G131" s="148"/>
-      <c r="H131" s="148"/>
-      <c r="I131" s="148"/>
-      <c r="J131" s="148"/>
-      <c r="K131" s="148"/>
-      <c r="L131" s="148"/>
-      <c r="M131" s="148"/>
-      <c r="N131" s="148"/>
-      <c r="O131" s="148"/>
-      <c r="P131" s="148"/>
-      <c r="Q131" s="148"/>
-      <c r="R131" s="148"/>
-      <c r="S131" s="148"/>
-      <c r="T131" s="148"/>
-      <c r="U131" s="148"/>
-      <c r="V131" s="148"/>
-      <c r="W131" s="148"/>
-      <c r="X131" s="148"/>
-      <c r="Y131" s="148"/>
-      <c r="Z131" s="148"/>
-      <c r="AA131" s="148"/>
-      <c r="AB131" s="148"/>
-      <c r="AC131" s="148"/>
-      <c r="AD131" s="148"/>
-      <c r="AE131" s="148"/>
-      <c r="AF131" s="148"/>
-      <c r="AG131" s="148"/>
-      <c r="AH131" s="148"/>
-      <c r="AI131" s="148"/>
-      <c r="AJ131" s="148"/>
-      <c r="AK131" s="148"/>
-      <c r="AL131" s="148"/>
-      <c r="AM131" s="148"/>
-      <c r="AN131" s="148"/>
-      <c r="AO131" s="148"/>
-      <c r="AP131" s="148"/>
-      <c r="AQ131" s="148"/>
-      <c r="AR131" s="149"/>
-    </row>
-    <row r="132" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="147"/>
-      <c r="B132" s="148"/>
-      <c r="C132" s="148"/>
-      <c r="D132" s="148"/>
-      <c r="E132" s="148"/>
-      <c r="F132" s="148"/>
-      <c r="G132" s="148"/>
-      <c r="H132" s="148"/>
-      <c r="I132" s="148"/>
-      <c r="J132" s="148"/>
-      <c r="K132" s="148"/>
-      <c r="L132" s="148"/>
-      <c r="M132" s="148"/>
-      <c r="N132" s="148"/>
-      <c r="O132" s="148"/>
-      <c r="P132" s="148"/>
-      <c r="Q132" s="148"/>
-      <c r="R132" s="148"/>
-      <c r="S132" s="148"/>
-      <c r="T132" s="148"/>
-      <c r="U132" s="148"/>
-      <c r="V132" s="148"/>
-      <c r="W132" s="148"/>
-      <c r="X132" s="148"/>
-      <c r="Y132" s="148"/>
-      <c r="Z132" s="148"/>
-      <c r="AA132" s="148"/>
-      <c r="AB132" s="148"/>
-      <c r="AC132" s="148"/>
-      <c r="AD132" s="148"/>
-      <c r="AE132" s="148"/>
-      <c r="AF132" s="148"/>
-      <c r="AG132" s="148"/>
-      <c r="AH132" s="148"/>
-      <c r="AI132" s="148"/>
-      <c r="AJ132" s="148"/>
-      <c r="AK132" s="148"/>
-      <c r="AL132" s="148"/>
-      <c r="AM132" s="148"/>
-      <c r="AN132" s="148"/>
-      <c r="AO132" s="148"/>
-      <c r="AP132" s="148"/>
-      <c r="AQ132" s="148"/>
-      <c r="AR132" s="149"/>
-    </row>
-    <row r="133" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="147"/>
-      <c r="B133" s="148"/>
-      <c r="C133" s="148"/>
-      <c r="D133" s="148"/>
-      <c r="E133" s="148"/>
-      <c r="F133" s="148"/>
-      <c r="G133" s="148"/>
-      <c r="H133" s="148"/>
-      <c r="I133" s="148"/>
-      <c r="J133" s="148"/>
-      <c r="K133" s="148"/>
-      <c r="L133" s="148"/>
-      <c r="M133" s="148"/>
-      <c r="N133" s="148"/>
-      <c r="O133" s="148"/>
-      <c r="P133" s="148"/>
-      <c r="Q133" s="148"/>
-      <c r="R133" s="148"/>
-      <c r="S133" s="148"/>
-      <c r="T133" s="148"/>
-      <c r="U133" s="148"/>
-      <c r="V133" s="148"/>
-      <c r="W133" s="148"/>
-      <c r="X133" s="148"/>
-      <c r="Y133" s="148"/>
-      <c r="Z133" s="148"/>
-      <c r="AA133" s="148"/>
-      <c r="AB133" s="148"/>
-      <c r="AC133" s="148"/>
-      <c r="AD133" s="148"/>
-      <c r="AE133" s="148"/>
-      <c r="AF133" s="148"/>
-      <c r="AG133" s="148"/>
-      <c r="AH133" s="148"/>
-      <c r="AI133" s="148"/>
-      <c r="AJ133" s="148"/>
-      <c r="AK133" s="148"/>
-      <c r="AL133" s="148"/>
-      <c r="AM133" s="148"/>
-      <c r="AN133" s="148"/>
-      <c r="AO133" s="148"/>
-      <c r="AP133" s="148"/>
-      <c r="AQ133" s="148"/>
-      <c r="AR133" s="149"/>
-    </row>
-    <row r="134" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="147"/>
-      <c r="B134" s="148"/>
-      <c r="C134" s="148"/>
-      <c r="D134" s="148"/>
-      <c r="E134" s="148"/>
-      <c r="F134" s="148"/>
-      <c r="G134" s="148"/>
-      <c r="H134" s="148"/>
-      <c r="I134" s="148"/>
-      <c r="J134" s="148"/>
-      <c r="K134" s="148"/>
-      <c r="L134" s="148"/>
-      <c r="M134" s="148"/>
-      <c r="N134" s="148"/>
-      <c r="O134" s="148"/>
-      <c r="P134" s="148"/>
-      <c r="Q134" s="148"/>
-      <c r="R134" s="148"/>
-      <c r="S134" s="148"/>
-      <c r="T134" s="148"/>
-      <c r="U134" s="148"/>
-      <c r="V134" s="148"/>
-      <c r="W134" s="148"/>
-      <c r="X134" s="148"/>
-      <c r="Y134" s="148"/>
-      <c r="Z134" s="148"/>
-      <c r="AA134" s="148"/>
-      <c r="AB134" s="148"/>
-      <c r="AC134" s="148"/>
-      <c r="AD134" s="148"/>
-      <c r="AE134" s="148"/>
-      <c r="AF134" s="148"/>
-      <c r="AG134" s="148"/>
-      <c r="AH134" s="148"/>
-      <c r="AI134" s="148"/>
-      <c r="AJ134" s="148"/>
-      <c r="AK134" s="148"/>
-      <c r="AL134" s="148"/>
-      <c r="AM134" s="148"/>
-      <c r="AN134" s="148"/>
-      <c r="AO134" s="148"/>
-      <c r="AP134" s="148"/>
-      <c r="AQ134" s="148"/>
-      <c r="AR134" s="149"/>
-    </row>
-    <row r="135" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="147"/>
-      <c r="B135" s="148"/>
-      <c r="C135" s="148"/>
-      <c r="D135" s="148"/>
-      <c r="E135" s="148"/>
-      <c r="F135" s="148"/>
-      <c r="G135" s="148"/>
-      <c r="H135" s="148"/>
-      <c r="I135" s="148"/>
-      <c r="J135" s="148"/>
-      <c r="K135" s="148"/>
-      <c r="L135" s="148"/>
-      <c r="M135" s="148"/>
-      <c r="N135" s="148"/>
-      <c r="O135" s="148"/>
-      <c r="P135" s="148"/>
-      <c r="Q135" s="148"/>
-      <c r="R135" s="148"/>
-      <c r="S135" s="148"/>
-      <c r="T135" s="148"/>
-      <c r="U135" s="148"/>
-      <c r="V135" s="148"/>
-      <c r="W135" s="148"/>
-      <c r="X135" s="148"/>
-      <c r="Y135" s="148"/>
-      <c r="Z135" s="148"/>
-      <c r="AA135" s="148"/>
-      <c r="AB135" s="148"/>
-      <c r="AC135" s="148"/>
-      <c r="AD135" s="148"/>
-      <c r="AE135" s="148"/>
-      <c r="AF135" s="148"/>
-      <c r="AG135" s="148"/>
-      <c r="AH135" s="148"/>
-      <c r="AI135" s="148"/>
-      <c r="AJ135" s="148"/>
-      <c r="AK135" s="148"/>
-      <c r="AL135" s="148"/>
-      <c r="AM135" s="148"/>
-      <c r="AN135" s="148"/>
-      <c r="AO135" s="148"/>
-      <c r="AP135" s="148"/>
-      <c r="AQ135" s="148"/>
-      <c r="AR135" s="149"/>
-    </row>
-    <row r="136" spans="1:44" ht="8.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="147"/>
-      <c r="B136" s="148"/>
-      <c r="C136" s="148"/>
-      <c r="D136" s="148"/>
-      <c r="E136" s="148"/>
-      <c r="F136" s="148"/>
-      <c r="G136" s="148"/>
-      <c r="H136" s="148"/>
-      <c r="I136" s="148"/>
-      <c r="J136" s="148"/>
-      <c r="K136" s="148"/>
-      <c r="L136" s="148"/>
-      <c r="M136" s="148"/>
-      <c r="N136" s="148"/>
-      <c r="O136" s="148"/>
-      <c r="P136" s="148"/>
-      <c r="Q136" s="148"/>
-      <c r="R136" s="148"/>
-      <c r="S136" s="148"/>
-      <c r="T136" s="148"/>
-      <c r="U136" s="148"/>
-      <c r="V136" s="148"/>
-      <c r="W136" s="148"/>
-      <c r="X136" s="148"/>
-      <c r="Y136" s="148"/>
-      <c r="Z136" s="148"/>
-      <c r="AA136" s="148"/>
-      <c r="AB136" s="148"/>
-      <c r="AC136" s="148"/>
-      <c r="AD136" s="148"/>
-      <c r="AE136" s="148"/>
-      <c r="AF136" s="148"/>
-      <c r="AG136" s="148"/>
-      <c r="AH136" s="148"/>
-      <c r="AI136" s="148"/>
-      <c r="AJ136" s="148"/>
-      <c r="AK136" s="148"/>
-      <c r="AL136" s="148"/>
-      <c r="AM136" s="148"/>
-      <c r="AN136" s="148"/>
-      <c r="AO136" s="148"/>
-      <c r="AP136" s="148"/>
-      <c r="AQ136" s="148"/>
-      <c r="AR136" s="149"/>
-    </row>
-    <row r="137" spans="1:44" ht="8.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="150"/>
-      <c r="B137" s="151"/>
-      <c r="C137" s="151"/>
-      <c r="D137" s="151"/>
-      <c r="E137" s="151"/>
-      <c r="F137" s="151"/>
-      <c r="G137" s="151"/>
-      <c r="H137" s="151"/>
-      <c r="I137" s="151"/>
-      <c r="J137" s="151"/>
-      <c r="K137" s="151"/>
-      <c r="L137" s="151"/>
-      <c r="M137" s="151"/>
-      <c r="N137" s="151"/>
-      <c r="O137" s="151"/>
-      <c r="P137" s="151"/>
-      <c r="Q137" s="151"/>
-      <c r="R137" s="151"/>
-      <c r="S137" s="151"/>
-      <c r="T137" s="151"/>
-      <c r="U137" s="151"/>
-      <c r="V137" s="151"/>
-      <c r="W137" s="151"/>
-      <c r="X137" s="151"/>
-      <c r="Y137" s="151"/>
-      <c r="Z137" s="151"/>
-      <c r="AA137" s="151"/>
-      <c r="AB137" s="151"/>
-      <c r="AC137" s="151"/>
-      <c r="AD137" s="151"/>
-      <c r="AE137" s="151"/>
-      <c r="AF137" s="151"/>
-      <c r="AG137" s="151"/>
-      <c r="AH137" s="151"/>
-      <c r="AI137" s="151"/>
-      <c r="AJ137" s="151"/>
-      <c r="AK137" s="151"/>
-      <c r="AL137" s="151"/>
-      <c r="AM137" s="151"/>
-      <c r="AN137" s="151"/>
-      <c r="AO137" s="151"/>
-      <c r="AP137" s="151"/>
-      <c r="AQ137" s="151"/>
-      <c r="AR137" s="152"/>
+    <row r="124" spans="1:44" ht="8.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="150"/>
+      <c r="B124" s="151"/>
+      <c r="C124" s="151"/>
+      <c r="D124" s="151"/>
+      <c r="E124" s="151"/>
+      <c r="F124" s="151"/>
+      <c r="G124" s="151"/>
+      <c r="H124" s="151"/>
+      <c r="I124" s="151"/>
+      <c r="J124" s="151"/>
+      <c r="K124" s="151"/>
+      <c r="L124" s="151"/>
+      <c r="M124" s="151"/>
+      <c r="N124" s="151"/>
+      <c r="O124" s="151"/>
+      <c r="P124" s="151"/>
+      <c r="Q124" s="151"/>
+      <c r="R124" s="151"/>
+      <c r="S124" s="151"/>
+      <c r="T124" s="151"/>
+      <c r="U124" s="151"/>
+      <c r="V124" s="151"/>
+      <c r="W124" s="151"/>
+      <c r="X124" s="151"/>
+      <c r="Y124" s="151"/>
+      <c r="Z124" s="151"/>
+      <c r="AA124" s="151"/>
+      <c r="AB124" s="151"/>
+      <c r="AC124" s="151"/>
+      <c r="AD124" s="151"/>
+      <c r="AE124" s="151"/>
+      <c r="AF124" s="151"/>
+      <c r="AG124" s="151"/>
+      <c r="AH124" s="151"/>
+      <c r="AI124" s="151"/>
+      <c r="AJ124" s="151"/>
+      <c r="AK124" s="151"/>
+      <c r="AL124" s="151"/>
+      <c r="AM124" s="151"/>
+      <c r="AN124" s="151"/>
+      <c r="AO124" s="151"/>
+      <c r="AP124" s="151"/>
+      <c r="AQ124" s="151"/>
+      <c r="AR124" s="152"/>
     </row>
   </sheetData>
   <mergeCells count="143">
@@ -7729,8 +7716,8 @@
     <mergeCell ref="AL40:AR40"/>
     <mergeCell ref="AI41:AR41"/>
     <mergeCell ref="AC42:AN42"/>
-    <mergeCell ref="A61:AR137"/>
-    <mergeCell ref="A58:AR60"/>
+    <mergeCell ref="A48:AR124"/>
+    <mergeCell ref="A45:AR47"/>
     <mergeCell ref="AB40:AK40"/>
     <mergeCell ref="O40:S40"/>
     <mergeCell ref="T40:Z40"/>
@@ -7746,7 +7733,16 @@
     <mergeCell ref="AC38:AR39"/>
     <mergeCell ref="AB41:AH41"/>
     <mergeCell ref="AC43:AR44"/>
-    <mergeCell ref="AP42:AR42"/>
+    <mergeCell ref="AC37:AN37"/>
+    <mergeCell ref="AP37:AR37"/>
+    <mergeCell ref="AH26:AO26"/>
+    <mergeCell ref="AB28:AG28"/>
+    <mergeCell ref="AH27:AO27"/>
+    <mergeCell ref="AH28:AO28"/>
+    <mergeCell ref="AH24:AO24"/>
+    <mergeCell ref="AH25:AO25"/>
+    <mergeCell ref="AH8:AO8"/>
+    <mergeCell ref="AB6:AG11"/>
     <mergeCell ref="AP11:AQ11"/>
     <mergeCell ref="AB33:AR34"/>
     <mergeCell ref="AB35:AB36"/>
@@ -7760,15 +7756,6 @@
     <mergeCell ref="AP4:AP5"/>
     <mergeCell ref="AQ4:AQ5"/>
     <mergeCell ref="AR4:AR5"/>
-    <mergeCell ref="AC37:AN37"/>
-    <mergeCell ref="AP37:AR37"/>
-    <mergeCell ref="AH26:AO26"/>
-    <mergeCell ref="AB28:AG28"/>
-    <mergeCell ref="AH27:AO27"/>
-    <mergeCell ref="AH28:AO28"/>
-    <mergeCell ref="AH24:AO24"/>
-    <mergeCell ref="AH25:AO25"/>
-    <mergeCell ref="AH8:AO8"/>
     <mergeCell ref="A44:J44"/>
     <mergeCell ref="K44:Z44"/>
     <mergeCell ref="A33:G33"/>
@@ -7817,7 +7804,6 @@
     <mergeCell ref="AH11:AO11"/>
     <mergeCell ref="AH7:AO7"/>
     <mergeCell ref="AH13:AO13"/>
-    <mergeCell ref="A43:J43"/>
     <mergeCell ref="AB30:AR30"/>
     <mergeCell ref="AH18:AO18"/>
     <mergeCell ref="AH14:AO14"/>
@@ -7841,7 +7827,7 @@
     <mergeCell ref="T12:Z12"/>
     <mergeCell ref="B13:Z13"/>
     <mergeCell ref="A28:Z28"/>
-    <mergeCell ref="AB6:AG11"/>
+    <mergeCell ref="AP42:AR42"/>
     <mergeCell ref="B16:G16"/>
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="AH19:AO19"/>
@@ -7865,6 +7851,7 @@
     <mergeCell ref="H35:N35"/>
     <mergeCell ref="O35:S35"/>
     <mergeCell ref="T35:Z35"/>
+    <mergeCell ref="A43:J43"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
